--- a/Data input - RegEco - L4L - Sumsel - 2026.xlsx
+++ b/Data input - RegEco - L4L - Sumsel - 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/Regional-Economy-GGP-Sumsel-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="836" documentId="8_{7502310D-9C21-47FE-9F85-D887AF9F69FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1B3A5A7-36BD-4C0B-B571-D7151A12F8A4}"/>
+  <xr:revisionPtr revIDLastSave="940" documentId="8_{7502310D-9C21-47FE-9F85-D887AF9F69FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF01E6F6-0F1A-465A-8DEB-395E9ED534FB}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="599" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="599" firstSheet="8" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IO_Table_2025(RAW)" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
     <sheet name="Concordance" sheetId="7" r:id="rId19"/>
     <sheet name="growth pdrb" sheetId="9" r:id="rId20"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -72,9 +72,10 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="2">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
@@ -85,16 +86,30 @@
       </extLst>
     </bk>
   </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+  </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2353" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2357" uniqueCount="517">
   <si>
     <t>Kode</t>
   </si>
@@ -1728,18 +1743,22 @@
   <si>
     <t>% yang diterapkan di Stype2</t>
   </si>
+  <si>
+    <t>Q4</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="7">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="0.000000"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -1802,7 +1821,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1875,6 +1894,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1926,15 +1951,15 @@
   </borders>
   <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1956,7 +1981,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1977,8 +2002,8 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
@@ -1994,7 +2019,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2010,16 +2035,21 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2267,7 +2297,7 @@
             <c:numRef>
               <c:f>Populasi!$B$2:$AA$2</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>8447760</c:v>
@@ -2442,7 +2472,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3129,6 +3159,64 @@
 </personList>
 </file>
 
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>13</v>
+    <v>3</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -3434,17 +3522,17 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:BQ64"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="82" bestFit="1" customWidth="1"/>
-    <col min="47" max="57" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="47" max="57" width="8.77734375" bestFit="1" customWidth="1"/>
     <col min="58" max="59" width="12" bestFit="1" customWidth="1"/>
-    <col min="60" max="61" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="60" max="61" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="63" max="63" width="12" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="8.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69" s="1" customFormat="1">
@@ -16798,10 +16886,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5E0AB6D-C28E-499E-898B-42B2FBC58F71}">
   <dimension ref="A1:AE67"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="35.1796875" customWidth="1"/>
-    <col min="13" max="13" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.21875" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -18603,27 +18691,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="20">
+    <row r="63" spans="1:29" ht="20.399999999999999">
       <c r="B63" s="50" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="20">
+    <row r="64" spans="1:29" ht="20.399999999999999">
       <c r="B64" s="50" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="65" spans="2:2" ht="22.5">
+    <row r="65" spans="2:2" ht="23.4">
       <c r="B65" s="49" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="66" spans="2:2" ht="30">
+    <row r="66" spans="2:2" ht="30.6">
       <c r="B66" s="49" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="67" spans="2:2" ht="20">
+    <row r="67" spans="2:2" ht="20.399999999999999">
       <c r="B67" s="51" t="s">
         <v>493</v>
       </c>
@@ -18635,12 +18723,12 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFAF8D53-00EB-4FEE-8CEB-3D3D74D6696F}">
-  <dimension ref="A1:AL101"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:AL118"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="82" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.54296875" customWidth="1"/>
-    <col min="4" max="5" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" customWidth="1"/>
+    <col min="4" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -18724,65 +18812,57 @@
       <c r="C2" s="32">
         <v>0</v>
       </c>
-      <c r="D2" s="32">
-        <v>0</v>
-      </c>
-      <c r="E2" s="32">
-        <v>0</v>
-      </c>
-      <c r="F2" s="32">
-        <v>0</v>
-      </c>
-      <c r="G2" s="32">
-        <v>0</v>
-      </c>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
       <c r="H2" s="3">
-        <v>1.0000000000000028E-2</v>
+        <v>4.0000000000000018E-3</v>
       </c>
       <c r="I2" s="3">
-        <v>1.6000000000000025E-2</v>
+        <v>4.0000000000000018E-3</v>
       </c>
       <c r="J2" s="3">
-        <v>2.200000000000002E-2</v>
+        <v>4.0000000000000018E-3</v>
       </c>
       <c r="K2" s="3">
-        <v>2.8000000000000018E-2</v>
+        <v>4.0000000000000018E-3</v>
       </c>
       <c r="L2" s="3">
-        <v>3.4000000000000016E-2</v>
+        <v>8.9706666666666685E-3</v>
       </c>
       <c r="M2" s="3">
-        <v>4.0000000000000008E-2</v>
+        <v>8.9706666666666685E-3</v>
       </c>
       <c r="N2" s="3">
-        <v>4.6000000000000006E-2</v>
+        <v>8.9706666666666685E-3</v>
       </c>
       <c r="O2" s="3">
-        <v>5.2000000000000005E-2</v>
+        <v>8.9706666666666685E-3</v>
       </c>
       <c r="P2" s="3">
-        <v>5.8000000000000003E-2</v>
+        <v>1.5136E-2</v>
       </c>
       <c r="Q2" s="3">
-        <v>6.4000000000000001E-2</v>
+        <v>1.5136E-2</v>
       </c>
       <c r="R2" s="3">
-        <v>6.9999999999999993E-2</v>
+        <v>1.5136E-2</v>
       </c>
       <c r="S2" s="3">
-        <v>7.5999999999999984E-2</v>
+        <v>1.5136E-2</v>
       </c>
       <c r="T2" s="3">
-        <v>8.199999999999999E-2</v>
+        <v>2.2495999999999999E-2</v>
       </c>
       <c r="U2" s="3">
-        <v>8.7999999999999981E-2</v>
+        <v>2.2495999999999999E-2</v>
       </c>
       <c r="V2" s="3">
-        <v>9.3999999999999986E-2</v>
+        <v>2.2495999999999999E-2</v>
       </c>
       <c r="W2" s="3">
-        <v>9.9999999999999978E-2</v>
+        <v>2.2495999999999999E-2</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -18795,66 +18875,26 @@
       <c r="C3" s="32">
         <v>0</v>
       </c>
-      <c r="D3" s="32">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32">
-        <v>0</v>
-      </c>
-      <c r="F3" s="32">
-        <v>0</v>
-      </c>
-      <c r="G3" s="32">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>1.0000000000000028E-2</v>
-      </c>
-      <c r="I3" s="3">
-        <v>1.6000000000000025E-2</v>
-      </c>
-      <c r="J3" s="3">
-        <v>2.200000000000002E-2</v>
-      </c>
-      <c r="K3" s="3">
-        <v>2.8000000000000018E-2</v>
-      </c>
-      <c r="L3" s="3">
-        <v>3.4000000000000016E-2</v>
-      </c>
-      <c r="M3" s="3">
-        <v>4.0000000000000008E-2</v>
-      </c>
-      <c r="N3" s="3">
-        <v>4.6000000000000006E-2</v>
-      </c>
-      <c r="O3" s="3">
-        <v>5.2000000000000005E-2</v>
-      </c>
-      <c r="P3" s="3">
-        <v>5.8000000000000003E-2</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>6.4000000000000001E-2</v>
-      </c>
-      <c r="R3" s="3">
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="S3" s="3">
-        <v>7.5999999999999984E-2</v>
-      </c>
-      <c r="T3" s="3">
-        <v>8.199999999999999E-2</v>
-      </c>
-      <c r="U3" s="3">
-        <v>8.7999999999999981E-2</v>
-      </c>
-      <c r="V3" s="3">
-        <v>9.3999999999999986E-2</v>
-      </c>
-      <c r="W3" s="3">
-        <v>9.9999999999999978E-2</v>
-      </c>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
     </row>
     <row r="4" spans="1:23">
       <c r="A4">
@@ -18866,65 +18906,57 @@
       <c r="C4" s="32">
         <v>0</v>
       </c>
-      <c r="D4" s="32">
-        <v>0</v>
-      </c>
-      <c r="E4" s="32">
-        <v>0</v>
-      </c>
-      <c r="F4" s="32">
-        <v>0</v>
-      </c>
-      <c r="G4" s="32">
-        <v>0</v>
-      </c>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
       <c r="H4" s="3">
-        <v>1.0000000000000028E-2</v>
+        <v>2.5500000000000028E-3</v>
       </c>
       <c r="I4" s="3">
-        <v>1.6000000000000025E-2</v>
+        <v>2.5500000000000028E-3</v>
       </c>
       <c r="J4" s="3">
-        <v>2.200000000000002E-2</v>
+        <v>2.5500000000000028E-3</v>
       </c>
       <c r="K4" s="3">
-        <v>2.8000000000000018E-2</v>
+        <v>2.5500000000000028E-3</v>
       </c>
       <c r="L4" s="3">
-        <v>3.4000000000000016E-2</v>
+        <v>1.2169555555555558E-2</v>
       </c>
       <c r="M4" s="3">
-        <v>4.0000000000000008E-2</v>
+        <v>1.2169555555555558E-2</v>
       </c>
       <c r="N4" s="3">
-        <v>4.6000000000000006E-2</v>
+        <v>1.2169555555555558E-2</v>
       </c>
       <c r="O4" s="3">
-        <v>5.2000000000000005E-2</v>
+        <v>1.2169555555555558E-2</v>
       </c>
       <c r="P4" s="3">
-        <v>5.8000000000000003E-2</v>
+        <v>2.8814888888888886E-2</v>
       </c>
       <c r="Q4" s="3">
-        <v>6.4000000000000001E-2</v>
+        <v>2.8814888888888886E-2</v>
       </c>
       <c r="R4" s="3">
-        <v>6.9999999999999993E-2</v>
+        <v>2.8814888888888886E-2</v>
       </c>
       <c r="S4" s="3">
-        <v>7.5999999999999984E-2</v>
+        <v>2.8814888888888886E-2</v>
       </c>
       <c r="T4" s="3">
-        <v>8.199999999999999E-2</v>
+        <v>5.2485999999999998E-2</v>
       </c>
       <c r="U4" s="3">
-        <v>8.7999999999999981E-2</v>
+        <v>5.2485999999999998E-2</v>
       </c>
       <c r="V4" s="3">
-        <v>9.3999999999999986E-2</v>
+        <v>5.2485999999999998E-2</v>
       </c>
       <c r="W4" s="3">
-        <v>9.9999999999999978E-2</v>
+        <v>5.2485999999999998E-2</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -18937,65 +18969,57 @@
       <c r="C5" s="32">
         <v>0</v>
       </c>
-      <c r="D5" s="32">
-        <v>0</v>
-      </c>
-      <c r="E5" s="32">
-        <v>0</v>
-      </c>
-      <c r="F5" s="32">
-        <v>0</v>
-      </c>
-      <c r="G5" s="32">
-        <v>0</v>
-      </c>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
       <c r="H5" s="3">
-        <v>1.0000000000000028E-2</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="I5" s="3">
-        <v>1.6000000000000025E-2</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="J5" s="3">
-        <v>2.200000000000002E-2</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="K5" s="3">
-        <v>2.8000000000000018E-2</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="L5" s="3">
-        <v>3.4000000000000016E-2</v>
+        <v>1.541511111111111E-2</v>
       </c>
       <c r="M5" s="3">
-        <v>4.0000000000000008E-2</v>
+        <v>1.541511111111111E-2</v>
       </c>
       <c r="N5" s="3">
-        <v>4.6000000000000006E-2</v>
+        <v>1.541511111111111E-2</v>
       </c>
       <c r="O5" s="3">
-        <v>5.2000000000000005E-2</v>
+        <v>1.541511111111111E-2</v>
       </c>
       <c r="P5" s="3">
-        <v>5.8000000000000003E-2</v>
+        <v>3.5393777777777774E-2</v>
       </c>
       <c r="Q5" s="3">
-        <v>6.4000000000000001E-2</v>
+        <v>3.5393777777777774E-2</v>
       </c>
       <c r="R5" s="3">
-        <v>6.9999999999999993E-2</v>
+        <v>3.5393777777777774E-2</v>
       </c>
       <c r="S5" s="3">
-        <v>7.5999999999999984E-2</v>
+        <v>3.5393777777777774E-2</v>
       </c>
       <c r="T5" s="3">
-        <v>8.199999999999999E-2</v>
+        <v>6.3535999999999995E-2</v>
       </c>
       <c r="U5" s="3">
-        <v>8.7999999999999981E-2</v>
+        <v>6.3535999999999995E-2</v>
       </c>
       <c r="V5" s="3">
-        <v>9.3999999999999986E-2</v>
+        <v>6.3535999999999995E-2</v>
       </c>
       <c r="W5" s="3">
-        <v>9.9999999999999978E-2</v>
+        <v>6.3535999999999995E-2</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -19008,65 +19032,57 @@
       <c r="C6" s="32">
         <v>0</v>
       </c>
-      <c r="D6" s="32">
-        <v>0</v>
-      </c>
-      <c r="E6" s="32">
-        <v>0</v>
-      </c>
-      <c r="F6" s="32">
-        <v>0</v>
-      </c>
-      <c r="G6" s="32">
-        <v>0</v>
-      </c>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="3">
-        <v>1.0000000000000028E-2</v>
+        <v>3.9809533183954061E-3</v>
       </c>
       <c r="I6" s="3">
-        <v>1.6000000000000025E-2</v>
+        <v>3.9809533183954061E-3</v>
       </c>
       <c r="J6" s="3">
-        <v>2.200000000000002E-2</v>
+        <v>3.9809533183954061E-3</v>
       </c>
       <c r="K6" s="3">
-        <v>2.8000000000000018E-2</v>
+        <v>3.9809533183954061E-3</v>
       </c>
       <c r="L6" s="3">
-        <v>3.4000000000000016E-2</v>
+        <v>1.5780792698487447E-2</v>
       </c>
       <c r="M6" s="3">
-        <v>4.0000000000000008E-2</v>
+        <v>1.5780792698487447E-2</v>
       </c>
       <c r="N6" s="3">
-        <v>4.6000000000000006E-2</v>
+        <v>1.5780792698487447E-2</v>
       </c>
       <c r="O6" s="3">
-        <v>5.2000000000000005E-2</v>
+        <v>1.5780792698487447E-2</v>
       </c>
       <c r="P6" s="3">
-        <v>5.8000000000000003E-2</v>
+        <v>3.4983230673732831E-2</v>
       </c>
       <c r="Q6" s="3">
-        <v>6.4000000000000001E-2</v>
+        <v>3.4983230673732831E-2</v>
       </c>
       <c r="R6" s="3">
-        <v>6.9999999999999993E-2</v>
+        <v>3.4983230673732831E-2</v>
       </c>
       <c r="S6" s="3">
-        <v>7.5999999999999984E-2</v>
+        <v>3.4983230673732831E-2</v>
       </c>
       <c r="T6" s="3">
-        <v>8.199999999999999E-2</v>
+        <v>6.1588267244131557E-2</v>
       </c>
       <c r="U6" s="3">
-        <v>8.7999999999999981E-2</v>
+        <v>6.1588267244131557E-2</v>
       </c>
       <c r="V6" s="3">
-        <v>9.3999999999999986E-2</v>
+        <v>6.1588267244131557E-2</v>
       </c>
       <c r="W6" s="3">
-        <v>9.9999999999999978E-2</v>
+        <v>6.1588267244131557E-2</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -19079,66 +19095,26 @@
       <c r="C7" s="32">
         <v>0</v>
       </c>
-      <c r="D7" s="32">
-        <v>0</v>
-      </c>
-      <c r="E7" s="32">
-        <v>0</v>
-      </c>
-      <c r="F7" s="32">
-        <v>0</v>
-      </c>
-      <c r="G7" s="32">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1.0000000000000028E-2</v>
-      </c>
-      <c r="I7" s="3">
-        <v>1.6000000000000025E-2</v>
-      </c>
-      <c r="J7" s="3">
-        <v>2.200000000000002E-2</v>
-      </c>
-      <c r="K7" s="3">
-        <v>2.8000000000000018E-2</v>
-      </c>
-      <c r="L7" s="3">
-        <v>3.4000000000000016E-2</v>
-      </c>
-      <c r="M7" s="3">
-        <v>4.0000000000000008E-2</v>
-      </c>
-      <c r="N7" s="3">
-        <v>4.6000000000000006E-2</v>
-      </c>
-      <c r="O7" s="3">
-        <v>5.2000000000000005E-2</v>
-      </c>
-      <c r="P7" s="3">
-        <v>5.8000000000000003E-2</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>6.4000000000000001E-2</v>
-      </c>
-      <c r="R7" s="3">
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="S7" s="3">
-        <v>7.5999999999999984E-2</v>
-      </c>
-      <c r="T7" s="3">
-        <v>8.199999999999999E-2</v>
-      </c>
-      <c r="U7" s="3">
-        <v>8.7999999999999981E-2</v>
-      </c>
-      <c r="V7" s="3">
-        <v>9.3999999999999986E-2</v>
-      </c>
-      <c r="W7" s="3">
-        <v>9.9999999999999978E-2</v>
-      </c>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
     </row>
     <row r="8" spans="1:23">
       <c r="A8">
@@ -19150,66 +19126,26 @@
       <c r="C8" s="32">
         <v>0</v>
       </c>
-      <c r="D8" s="32">
-        <v>0</v>
-      </c>
-      <c r="E8" s="32">
-        <v>0</v>
-      </c>
-      <c r="F8" s="32">
-        <v>0</v>
-      </c>
-      <c r="G8" s="32">
-        <v>0</v>
-      </c>
-      <c r="H8" s="32">
-        <v>0</v>
-      </c>
-      <c r="I8" s="32">
-        <v>0</v>
-      </c>
-      <c r="J8" s="32">
-        <v>0</v>
-      </c>
-      <c r="K8" s="32">
-        <v>0</v>
-      </c>
-      <c r="L8" s="32">
-        <v>0</v>
-      </c>
-      <c r="M8" s="32">
-        <v>0</v>
-      </c>
-      <c r="N8" s="32">
-        <v>0</v>
-      </c>
-      <c r="O8" s="32">
-        <v>0</v>
-      </c>
-      <c r="P8" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="32">
-        <v>0</v>
-      </c>
-      <c r="R8" s="32">
-        <v>0</v>
-      </c>
-      <c r="S8" s="32">
-        <v>0</v>
-      </c>
-      <c r="T8" s="32">
-        <v>0</v>
-      </c>
-      <c r="U8" s="32">
-        <v>0</v>
-      </c>
-      <c r="V8" s="32">
-        <v>0</v>
-      </c>
-      <c r="W8" s="32">
-        <v>0</v>
-      </c>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="32"/>
+      <c r="S8" s="32"/>
+      <c r="T8" s="32"/>
+      <c r="U8" s="32"/>
+      <c r="V8" s="32"/>
+      <c r="W8" s="32"/>
     </row>
     <row r="9" spans="1:23">
       <c r="A9">
@@ -19221,66 +19157,26 @@
       <c r="C9" s="32">
         <v>0</v>
       </c>
-      <c r="D9" s="32">
-        <v>0</v>
-      </c>
-      <c r="E9" s="32">
-        <v>0</v>
-      </c>
-      <c r="F9" s="32">
-        <v>0</v>
-      </c>
-      <c r="G9" s="32">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1.0000000000000028E-2</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1.6000000000000025E-2</v>
-      </c>
-      <c r="J9" s="3">
-        <v>2.200000000000002E-2</v>
-      </c>
-      <c r="K9" s="3">
-        <v>2.8000000000000018E-2</v>
-      </c>
-      <c r="L9" s="3">
-        <v>3.4000000000000016E-2</v>
-      </c>
-      <c r="M9" s="3">
-        <v>4.0000000000000008E-2</v>
-      </c>
-      <c r="N9" s="3">
-        <v>4.6000000000000006E-2</v>
-      </c>
-      <c r="O9" s="3">
-        <v>5.2000000000000005E-2</v>
-      </c>
-      <c r="P9" s="3">
-        <v>5.8000000000000003E-2</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>6.4000000000000001E-2</v>
-      </c>
-      <c r="R9" s="3">
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="S9" s="3">
-        <v>7.5999999999999984E-2</v>
-      </c>
-      <c r="T9" s="3">
-        <v>8.199999999999999E-2</v>
-      </c>
-      <c r="U9" s="3">
-        <v>8.7999999999999981E-2</v>
-      </c>
-      <c r="V9" s="3">
-        <v>9.3999999999999986E-2</v>
-      </c>
-      <c r="W9" s="3">
-        <v>9.9999999999999978E-2</v>
-      </c>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
     </row>
     <row r="10" spans="1:23">
       <c r="A10">
@@ -19292,65 +19188,57 @@
       <c r="C10" s="32">
         <v>0</v>
       </c>
-      <c r="D10" s="32">
-        <v>0</v>
-      </c>
-      <c r="E10" s="32">
-        <v>0</v>
-      </c>
-      <c r="F10" s="32">
-        <v>0</v>
-      </c>
-      <c r="G10" s="32">
-        <v>0</v>
-      </c>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
       <c r="H10" s="3">
-        <v>1.0000000000000028E-2</v>
+        <v>3.2000000000000015E-3</v>
       </c>
       <c r="I10" s="3">
-        <v>1.6000000000000025E-2</v>
+        <v>4.100266666666668E-3</v>
       </c>
       <c r="J10" s="3">
-        <v>2.200000000000002E-2</v>
+        <v>5.0005333333333355E-3</v>
       </c>
       <c r="K10" s="3">
-        <v>2.8000000000000018E-2</v>
+        <v>5.9008000000000021E-3</v>
       </c>
       <c r="L10" s="3">
-        <v>3.4000000000000016E-2</v>
+        <v>6.8010666666666686E-3</v>
       </c>
       <c r="M10" s="3">
-        <v>4.0000000000000008E-2</v>
+        <v>7.7013333333333361E-3</v>
       </c>
       <c r="N10" s="3">
-        <v>4.6000000000000006E-2</v>
+        <v>8.6016000000000026E-3</v>
       </c>
       <c r="O10" s="3">
-        <v>5.2000000000000005E-2</v>
+        <v>9.5018666666666692E-3</v>
       </c>
       <c r="P10" s="3">
-        <v>5.8000000000000003E-2</v>
+        <v>1.0402133333333336E-2</v>
       </c>
       <c r="Q10" s="3">
-        <v>6.4000000000000001E-2</v>
+        <v>1.1302400000000002E-2</v>
       </c>
       <c r="R10" s="3">
-        <v>6.9999999999999993E-2</v>
+        <v>1.2202666666666669E-2</v>
       </c>
       <c r="S10" s="3">
-        <v>7.5999999999999984E-2</v>
+        <v>1.3102933333333337E-2</v>
       </c>
       <c r="T10" s="3">
-        <v>8.199999999999999E-2</v>
+        <v>1.4003200000000004E-2</v>
       </c>
       <c r="U10" s="3">
-        <v>8.7999999999999981E-2</v>
+        <v>1.490346666666667E-2</v>
       </c>
       <c r="V10" s="3">
-        <v>9.3999999999999986E-2</v>
+        <v>1.5803733333333337E-2</v>
       </c>
       <c r="W10" s="3">
-        <v>9.9999999999999978E-2</v>
+        <v>1.6704000000000004E-2</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -22705,7 +22593,7 @@
       </c>
     </row>
     <row r="60" spans="1:38">
-      <c r="B60" s="54" t="s">
+      <c r="B60" s="52" t="s">
         <v>503</v>
       </c>
       <c r="C60" t="s">
@@ -22803,7 +22691,7 @@
       </c>
     </row>
     <row r="61" spans="1:38">
-      <c r="B61" s="54"/>
+      <c r="B61" s="52"/>
       <c r="C61" s="33" t="s">
         <v>511</v>
       </c>
@@ -22897,9 +22785,21 @@
       <c r="AG61">
         <v>20770676.324936479</v>
       </c>
+      <c r="AI61" t="s">
+        <v>461</v>
+      </c>
+      <c r="AJ61" t="s">
+        <v>462</v>
+      </c>
+      <c r="AK61" t="s">
+        <v>463</v>
+      </c>
+      <c r="AL61" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="62" spans="1:38">
-      <c r="B62" s="54"/>
+      <c r="B62" s="52"/>
       <c r="C62" s="4" t="s">
         <v>512</v>
       </c>
@@ -22939,7 +22839,7 @@
         <f t="shared" si="0"/>
         <v>0.55951225939955829</v>
       </c>
-      <c r="M62" s="55">
+      <c r="M62" s="53">
         <f t="shared" si="0"/>
         <v>7.9619066367907956E-2</v>
       </c>
@@ -22983,7 +22883,7 @@
         <f t="shared" si="0"/>
         <v>0.27157961575453177</v>
       </c>
-      <c r="X62" s="55">
+      <c r="X62" s="53">
         <f t="shared" si="0"/>
         <v>0.49333106227327328</v>
       </c>
@@ -23041,137 +22941,185 @@
       </c>
     </row>
     <row r="63" spans="1:38">
-      <c r="B63" s="54"/>
+      <c r="B63" s="52"/>
       <c r="C63" s="23" t="s">
         <v>513</v>
       </c>
       <c r="H63" s="40">
-        <v>7.9619066367908053E-2</v>
+        <v>7.9619066367908081E-2</v>
       </c>
       <c r="I63" s="40">
-        <v>0.11364446194338083</v>
+        <v>0.10631112861004754</v>
       </c>
       <c r="J63" s="40">
-        <v>0.14766985751885361</v>
+        <v>0.13300319085218698</v>
       </c>
       <c r="K63" s="40">
-        <v>0.18169525309432641</v>
+        <v>0.15969525309432647</v>
       </c>
       <c r="L63" s="40">
-        <v>0.2157206486697992</v>
+        <v>0.18638731533646591</v>
       </c>
       <c r="M63" s="40">
-        <v>0.24974604424527197</v>
+        <v>0.21307937757860537</v>
       </c>
       <c r="N63" s="40">
-        <v>0.28377143982074476</v>
+        <v>0.23977143982074484</v>
       </c>
       <c r="O63" s="40">
-        <v>0.31779683539621756</v>
+        <v>0.26646350206288427</v>
       </c>
       <c r="P63" s="40">
-        <v>0.35182223097169035</v>
+        <v>0.29315556430502376</v>
       </c>
       <c r="Q63" s="40">
-        <v>0.38584762654716315</v>
+        <v>0.3198476265471632</v>
       </c>
       <c r="R63" s="40">
-        <v>0.41987302212263594</v>
+        <v>0.34653968878930269</v>
       </c>
       <c r="S63" s="40">
-        <v>0.45389841769810868</v>
+        <v>0.37323175103144213</v>
       </c>
       <c r="T63" s="40">
-        <v>0.48792381327358147</v>
+        <v>0.39992381327358162</v>
       </c>
       <c r="U63" s="40">
-        <v>0.52194920884905427</v>
+        <v>0.42661587551572105</v>
       </c>
       <c r="V63" s="40">
-        <v>0.55597460442452706</v>
+        <v>0.45330793775786055</v>
       </c>
       <c r="W63" s="40">
-        <v>0.58999999999999986</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="64" spans="1:38">
-      <c r="B64" s="54"/>
+      <c r="B64" s="52"/>
       <c r="C64" t="s">
         <v>514</v>
       </c>
+      <c r="H64" s="40">
+        <v>5.0000000000000024E-2</v>
+      </c>
+      <c r="I64" s="40">
+        <v>5.8666666666666686E-2</v>
+      </c>
+      <c r="J64" s="40">
+        <v>6.7333333333333356E-2</v>
+      </c>
+      <c r="K64" s="40">
+        <v>7.6000000000000012E-2</v>
+      </c>
+      <c r="L64" s="40">
+        <v>8.4666666666666668E-2</v>
+      </c>
+      <c r="M64" s="40">
+        <v>9.3333333333333338E-2</v>
+      </c>
+      <c r="N64" s="40">
+        <v>0.10200000000000001</v>
+      </c>
+      <c r="O64" s="40">
+        <v>0.11066666666666666</v>
+      </c>
+      <c r="P64" s="40">
+        <v>0.11933333333333332</v>
+      </c>
+      <c r="Q64" s="40">
+        <v>0.128</v>
+      </c>
+      <c r="R64" s="40">
+        <v>0.13666666666666666</v>
+      </c>
+      <c r="S64" s="40">
+        <v>0.14533333333333331</v>
+      </c>
+      <c r="T64" s="40">
+        <v>0.15399999999999997</v>
+      </c>
+      <c r="U64" s="40">
+        <v>0.16266666666666663</v>
+      </c>
+      <c r="V64" s="40">
+        <v>0.17133333333333331</v>
+      </c>
+      <c r="W64" s="40">
+        <v>0.17999999999999997</v>
+      </c>
     </row>
     <row r="65" spans="2:38">
-      <c r="B65" s="54"/>
+      <c r="B65" s="52"/>
       <c r="C65" s="34" t="s">
         <v>515</v>
       </c>
-      <c r="H65">
+      <c r="H65" s="55">
         <f>H63*H64</f>
-        <v>0</v>
-      </c>
-      <c r="I65">
+        <v>3.9809533183954061E-3</v>
+      </c>
+      <c r="I65" s="55">
         <f>H65</f>
-        <v>0</v>
-      </c>
-      <c r="J65">
+        <v>3.9809533183954061E-3</v>
+      </c>
+      <c r="J65" s="55">
         <f t="shared" ref="J65:K65" si="1">I65</f>
-        <v>0</v>
-      </c>
-      <c r="K65">
+        <v>3.9809533183954061E-3</v>
+      </c>
+      <c r="K65" s="55">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L65">
+        <v>3.9809533183954061E-3</v>
+      </c>
+      <c r="L65" s="55">
         <f>L63*L64</f>
-        <v>0</v>
-      </c>
-      <c r="M65">
+        <v>1.5780792698487447E-2</v>
+      </c>
+      <c r="M65" s="55">
         <f>L65</f>
-        <v>0</v>
-      </c>
-      <c r="N65">
+        <v>1.5780792698487447E-2</v>
+      </c>
+      <c r="N65" s="55">
         <f t="shared" ref="N65:O65" si="2">M65</f>
-        <v>0</v>
-      </c>
-      <c r="O65">
+        <v>1.5780792698487447E-2</v>
+      </c>
+      <c r="O65" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P65">
+        <v>1.5780792698487447E-2</v>
+      </c>
+      <c r="P65" s="55">
         <f>P63*P64</f>
-        <v>0</v>
-      </c>
-      <c r="Q65">
+        <v>3.4983230673732831E-2</v>
+      </c>
+      <c r="Q65" s="55">
         <f>P65</f>
-        <v>0</v>
-      </c>
-      <c r="R65">
+        <v>3.4983230673732831E-2</v>
+      </c>
+      <c r="R65" s="55">
         <f t="shared" ref="R65:S65" si="3">Q65</f>
-        <v>0</v>
-      </c>
-      <c r="S65">
+        <v>3.4983230673732831E-2</v>
+      </c>
+      <c r="S65" s="55">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T65">
+        <v>3.4983230673732831E-2</v>
+      </c>
+      <c r="T65" s="55">
         <f>T63*T64</f>
-        <v>0</v>
-      </c>
-      <c r="U65">
+        <v>6.1588267244131557E-2</v>
+      </c>
+      <c r="U65" s="55">
         <f>T65</f>
-        <v>0</v>
-      </c>
-      <c r="V65">
+        <v>6.1588267244131557E-2</v>
+      </c>
+      <c r="V65" s="55">
         <f t="shared" ref="V65:W65" si="4">U65</f>
-        <v>0</v>
-      </c>
-      <c r="W65">
+        <v>6.1588267244131557E-2</v>
+      </c>
+      <c r="W65" s="55">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.1588267244131557E-2</v>
       </c>
     </row>
     <row r="66" spans="2:38">
-      <c r="B66" s="54" t="s">
+      <c r="B66" s="52" t="s">
         <v>504</v>
       </c>
       <c r="C66" t="s">
@@ -23269,7 +23217,7 @@
       </c>
     </row>
     <row r="67" spans="2:38">
-      <c r="B67" s="54"/>
+      <c r="B67" s="52"/>
       <c r="C67" s="33" t="s">
         <v>511</v>
       </c>
@@ -23365,7 +23313,7 @@
       </c>
     </row>
     <row r="68" spans="2:38">
-      <c r="B68" s="54"/>
+      <c r="B68" s="52"/>
       <c r="C68" s="4" t="s">
         <v>512</v>
       </c>
@@ -23413,79 +23361,79 @@
         <f t="shared" si="5"/>
         <v>0.11077424471870202</v>
       </c>
-      <c r="O68" s="56">
+      <c r="O68" s="54">
         <f t="shared" si="5"/>
         <v>2.4241411351035837E-2</v>
       </c>
-      <c r="P68" s="56">
+      <c r="P68" s="54">
         <f t="shared" si="5"/>
         <v>9.9654260526441871E-2</v>
       </c>
-      <c r="Q68" s="56">
+      <c r="Q68" s="54">
         <f t="shared" si="5"/>
         <v>0.20092313182958477</v>
       </c>
-      <c r="R68" s="56">
+      <c r="R68" s="54">
         <f t="shared" si="5"/>
         <v>0.15969733278317225</v>
       </c>
-      <c r="S68" s="56">
+      <c r="S68" s="54">
         <f t="shared" si="5"/>
         <v>0.12760198219149152</v>
       </c>
-      <c r="T68" s="56">
+      <c r="T68" s="54">
         <f t="shared" si="5"/>
         <v>0.38859607941980689</v>
       </c>
-      <c r="U68" s="56">
+      <c r="U68" s="54">
         <f t="shared" si="5"/>
         <v>0.54667244459277398</v>
       </c>
-      <c r="V68" s="56">
+      <c r="V68" s="54">
         <f t="shared" si="5"/>
         <v>0.20697444080792921</v>
       </c>
-      <c r="W68" s="56">
+      <c r="W68" s="54">
         <f t="shared" si="5"/>
         <v>0.61209167952352483</v>
       </c>
-      <c r="X68" s="56">
+      <c r="X68" s="54">
         <f t="shared" si="5"/>
         <v>0.49110384197837581</v>
       </c>
-      <c r="Y68" s="56">
+      <c r="Y68" s="54">
         <f t="shared" si="5"/>
         <v>0.23136219192907212</v>
       </c>
-      <c r="Z68" s="56">
+      <c r="Z68" s="54">
         <f t="shared" si="5"/>
         <v>0.44706693840362016</v>
       </c>
-      <c r="AA68" s="56">
+      <c r="AA68" s="54">
         <f t="shared" si="5"/>
         <v>0.63742628667594647</v>
       </c>
-      <c r="AB68" s="56">
+      <c r="AB68" s="54">
         <f t="shared" si="5"/>
         <v>0.20252742464218884</v>
       </c>
-      <c r="AC68" s="56">
+      <c r="AC68" s="54">
         <f t="shared" si="5"/>
         <v>0.5800516509118967</v>
       </c>
-      <c r="AD68" s="56">
+      <c r="AD68" s="54">
         <f t="shared" si="5"/>
         <v>0.66452388006852248</v>
       </c>
-      <c r="AE68" s="56">
+      <c r="AE68" s="54">
         <f t="shared" si="5"/>
         <v>0.27092063719180937</v>
       </c>
-      <c r="AF68" s="56">
+      <c r="AF68" s="54">
         <f t="shared" si="5"/>
         <v>0.57327885646240717</v>
       </c>
-      <c r="AG68" s="56">
+      <c r="AG68" s="54">
         <f t="shared" si="5"/>
         <v>0.52226571921484388</v>
       </c>
@@ -23507,137 +23455,185 @@
       </c>
     </row>
     <row r="69" spans="2:38">
-      <c r="B69" s="54"/>
+      <c r="B69" s="52"/>
       <c r="C69" s="23" t="s">
         <v>513</v>
       </c>
       <c r="H69" s="40">
-        <v>0.11000000000000003</v>
+        <v>0.11000000000000004</v>
       </c>
       <c r="I69" s="40">
-        <v>0.14266666666666669</v>
+        <v>0.12066666666666671</v>
       </c>
       <c r="J69" s="40">
-        <v>0.17533333333333334</v>
+        <v>0.13133333333333339</v>
       </c>
       <c r="K69" s="40">
-        <v>0.20800000000000002</v>
+        <v>0.14200000000000004</v>
       </c>
       <c r="L69" s="40">
-        <v>0.2406666666666667</v>
+        <v>0.1526666666666667</v>
       </c>
       <c r="M69" s="40">
-        <v>0.27333333333333332</v>
+        <v>0.16333333333333339</v>
       </c>
       <c r="N69" s="40">
-        <v>0.30599999999999999</v>
+        <v>0.17400000000000004</v>
       </c>
       <c r="O69" s="40">
-        <v>0.33866666666666667</v>
+        <v>0.1846666666666667</v>
       </c>
       <c r="P69" s="40">
-        <v>0.37133333333333335</v>
+        <v>0.19533333333333336</v>
       </c>
       <c r="Q69" s="40">
-        <v>0.40400000000000003</v>
+        <v>0.20600000000000002</v>
       </c>
       <c r="R69" s="40">
-        <v>0.43666666666666665</v>
+        <v>0.2166666666666667</v>
       </c>
       <c r="S69" s="40">
-        <v>0.46933333333333332</v>
+        <v>0.22733333333333336</v>
       </c>
       <c r="T69" s="40">
-        <v>0.502</v>
+        <v>0.23800000000000002</v>
       </c>
       <c r="U69" s="40">
-        <v>0.53466666666666662</v>
+        <v>0.2486666666666667</v>
       </c>
       <c r="V69" s="40">
-        <v>0.56733333333333325</v>
+        <v>0.25933333333333336</v>
       </c>
       <c r="W69" s="40">
-        <v>0.6</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="70" spans="2:38">
-      <c r="B70" s="54"/>
+      <c r="B70" s="52"/>
       <c r="C70" t="s">
         <v>514</v>
       </c>
+      <c r="H70" s="40">
+        <v>3.000000000000002E-2</v>
+      </c>
+      <c r="I70" s="40">
+        <v>3.8666666666666683E-2</v>
+      </c>
+      <c r="J70" s="40">
+        <v>4.7333333333333352E-2</v>
+      </c>
+      <c r="K70" s="40">
+        <v>5.6000000000000015E-2</v>
+      </c>
+      <c r="L70" s="40">
+        <v>6.4666666666666678E-2</v>
+      </c>
+      <c r="M70" s="40">
+        <v>7.3333333333333348E-2</v>
+      </c>
+      <c r="N70" s="40">
+        <v>8.2000000000000017E-2</v>
+      </c>
+      <c r="O70" s="40">
+        <v>9.0666666666666673E-2</v>
+      </c>
+      <c r="P70" s="40">
+        <v>9.9333333333333343E-2</v>
+      </c>
+      <c r="Q70" s="40">
+        <v>0.108</v>
+      </c>
+      <c r="R70" s="40">
+        <v>0.11666666666666667</v>
+      </c>
+      <c r="S70" s="40">
+        <v>0.12533333333333335</v>
+      </c>
+      <c r="T70" s="40">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="U70" s="40">
+        <v>0.14266666666666666</v>
+      </c>
+      <c r="V70" s="40">
+        <v>0.15133333333333332</v>
+      </c>
+      <c r="W70" s="40">
+        <v>0.15999999999999998</v>
+      </c>
     </row>
     <row r="71" spans="2:38">
-      <c r="B71" s="54"/>
+      <c r="B71" s="52"/>
       <c r="C71" s="34" t="s">
         <v>515</v>
       </c>
-      <c r="H71">
+      <c r="H71" s="55">
         <f>H69*H70</f>
-        <v>0</v>
-      </c>
-      <c r="I71">
+        <v>3.3000000000000035E-3</v>
+      </c>
+      <c r="I71" s="55">
         <f>H71</f>
-        <v>0</v>
-      </c>
-      <c r="J71">
+        <v>3.3000000000000035E-3</v>
+      </c>
+      <c r="J71" s="55">
         <f t="shared" ref="J71:K71" si="6">I71</f>
-        <v>0</v>
-      </c>
-      <c r="K71">
+        <v>3.3000000000000035E-3</v>
+      </c>
+      <c r="K71" s="55">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L71">
+        <v>3.3000000000000035E-3</v>
+      </c>
+      <c r="L71" s="55">
         <f>L69*L70</f>
-        <v>0</v>
-      </c>
-      <c r="M71">
+        <v>9.8724444444444476E-3</v>
+      </c>
+      <c r="M71" s="55">
         <f>L71</f>
-        <v>0</v>
-      </c>
-      <c r="N71">
+        <v>9.8724444444444476E-3</v>
+      </c>
+      <c r="N71" s="55">
         <f t="shared" ref="N71:O71" si="7">M71</f>
-        <v>0</v>
-      </c>
-      <c r="O71">
+        <v>9.8724444444444476E-3</v>
+      </c>
+      <c r="O71" s="55">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="P71">
+        <v>9.8724444444444476E-3</v>
+      </c>
+      <c r="P71" s="55">
         <f>P69*P70</f>
-        <v>0</v>
-      </c>
-      <c r="Q71">
+        <v>1.9403111111111114E-2</v>
+      </c>
+      <c r="Q71" s="55">
         <f>P71</f>
-        <v>0</v>
-      </c>
-      <c r="R71">
+        <v>1.9403111111111114E-2</v>
+      </c>
+      <c r="R71" s="55">
         <f t="shared" ref="R71:S71" si="8">Q71</f>
-        <v>0</v>
-      </c>
-      <c r="S71">
+        <v>1.9403111111111114E-2</v>
+      </c>
+      <c r="S71" s="55">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="T71">
+        <v>1.9403111111111114E-2</v>
+      </c>
+      <c r="T71" s="55">
         <f>T69*T70</f>
-        <v>0</v>
-      </c>
-      <c r="U71">
+        <v>3.1892000000000004E-2</v>
+      </c>
+      <c r="U71" s="55">
         <f>T71</f>
-        <v>0</v>
-      </c>
-      <c r="V71">
+        <v>3.1892000000000004E-2</v>
+      </c>
+      <c r="V71" s="55">
         <f t="shared" ref="V71:W71" si="9">U71</f>
-        <v>0</v>
-      </c>
-      <c r="W71">
+        <v>3.1892000000000004E-2</v>
+      </c>
+      <c r="W71" s="55">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3.1892000000000004E-2</v>
       </c>
     </row>
     <row r="72" spans="2:38">
-      <c r="B72" s="54" t="s">
+      <c r="B72" s="52" t="s">
         <v>505</v>
       </c>
       <c r="C72" t="s">
@@ -23735,7 +23731,7 @@
       </c>
     </row>
     <row r="73" spans="2:38">
-      <c r="B73" s="54"/>
+      <c r="B73" s="52"/>
       <c r="C73" s="33" t="s">
         <v>511</v>
       </c>
@@ -23831,7 +23827,7 @@
       </c>
     </row>
     <row r="74" spans="2:38">
-      <c r="B74" s="54"/>
+      <c r="B74" s="52"/>
       <c r="C74" s="4" t="s">
         <v>512</v>
       </c>
@@ -23951,7 +23947,7 @@
         <f t="shared" si="10"/>
         <v>0.19678768572099792</v>
       </c>
-      <c r="AG74" s="55">
+      <c r="AG74" s="53">
         <f t="shared" si="10"/>
         <v>6.2249484189112962E-2</v>
       </c>
@@ -23973,7 +23969,7 @@
       </c>
     </row>
     <row r="75" spans="2:38">
-      <c r="B75" s="54"/>
+      <c r="B75" s="52"/>
       <c r="C75" s="23" t="s">
         <v>513</v>
       </c>
@@ -24027,83 +24023,131 @@
       </c>
     </row>
     <row r="76" spans="2:38">
-      <c r="B76" s="54"/>
+      <c r="B76" s="52"/>
       <c r="C76" t="s">
         <v>514</v>
       </c>
+      <c r="H76" s="40">
+        <v>3.0000000000000006E-2</v>
+      </c>
+      <c r="I76" s="40">
+        <v>3.8000000000000006E-2</v>
+      </c>
+      <c r="J76" s="40">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="K76" s="40">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="L76" s="40">
+        <v>6.2E-2</v>
+      </c>
+      <c r="M76" s="40">
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="N76" s="40">
+        <v>7.7999999999999986E-2</v>
+      </c>
+      <c r="O76" s="40">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="P76" s="40">
+        <v>9.3999999999999986E-2</v>
+      </c>
+      <c r="Q76" s="40">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="R76" s="40">
+        <v>0.10999999999999999</v>
+      </c>
+      <c r="S76" s="40">
+        <v>0.11799999999999998</v>
+      </c>
+      <c r="T76" s="40">
+        <v>0.126</v>
+      </c>
+      <c r="U76" s="40">
+        <v>0.13399999999999998</v>
+      </c>
+      <c r="V76" s="40">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="W76" s="40">
+        <v>0.14999999999999997</v>
+      </c>
     </row>
     <row r="77" spans="2:38">
-      <c r="B77" s="54"/>
+      <c r="B77" s="52"/>
       <c r="C77" s="34" t="s">
         <v>515</v>
       </c>
-      <c r="H77">
+      <c r="H77" s="55">
         <f>H75*H76</f>
-        <v>0</v>
-      </c>
-      <c r="I77">
+        <v>1.8000000000000017E-3</v>
+      </c>
+      <c r="I77" s="55">
         <f>H77</f>
-        <v>0</v>
-      </c>
-      <c r="J77">
+        <v>1.8000000000000017E-3</v>
+      </c>
+      <c r="J77" s="55">
         <f t="shared" ref="J77:K77" si="11">I77</f>
-        <v>0</v>
-      </c>
-      <c r="K77">
+        <v>1.8000000000000017E-3</v>
+      </c>
+      <c r="K77" s="55">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L77">
+        <v>1.8000000000000017E-3</v>
+      </c>
+      <c r="L77" s="55">
         <f>L75*L76</f>
-        <v>0</v>
-      </c>
-      <c r="M77">
+        <v>1.4466666666666669E-2</v>
+      </c>
+      <c r="M77" s="55">
         <f>L77</f>
-        <v>0</v>
-      </c>
-      <c r="N77">
+        <v>1.4466666666666669E-2</v>
+      </c>
+      <c r="N77" s="55">
         <f t="shared" ref="N77:O77" si="12">M77</f>
-        <v>0</v>
-      </c>
-      <c r="O77">
+        <v>1.4466666666666669E-2</v>
+      </c>
+      <c r="O77" s="55">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="P77">
+        <v>1.4466666666666669E-2</v>
+      </c>
+      <c r="P77" s="55">
         <f>P75*P76</f>
-        <v>0</v>
-      </c>
-      <c r="Q77">
+        <v>3.8226666666666659E-2</v>
+      </c>
+      <c r="Q77" s="55">
         <f>P77</f>
-        <v>0</v>
-      </c>
-      <c r="R77">
+        <v>3.8226666666666659E-2</v>
+      </c>
+      <c r="R77" s="55">
         <f t="shared" ref="R77:S77" si="13">Q77</f>
-        <v>0</v>
-      </c>
-      <c r="S77">
+        <v>3.8226666666666659E-2</v>
+      </c>
+      <c r="S77" s="55">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T77">
+        <v>3.8226666666666659E-2</v>
+      </c>
+      <c r="T77" s="55">
         <f>T75*T76</f>
-        <v>0</v>
-      </c>
-      <c r="U77">
+        <v>7.3079999999999992E-2</v>
+      </c>
+      <c r="U77" s="55">
         <f>T77</f>
-        <v>0</v>
-      </c>
-      <c r="V77">
+        <v>7.3079999999999992E-2</v>
+      </c>
+      <c r="V77" s="55">
         <f t="shared" ref="V77:W77" si="14">U77</f>
-        <v>0</v>
-      </c>
-      <c r="W77">
+        <v>7.3079999999999992E-2</v>
+      </c>
+      <c r="W77" s="55">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>7.3079999999999992E-2</v>
       </c>
     </row>
     <row r="78" spans="2:38">
-      <c r="B78" s="54" t="s">
+      <c r="B78" s="52" t="s">
         <v>506</v>
       </c>
       <c r="C78" t="s">
@@ -24186,7 +24230,7 @@
       </c>
     </row>
     <row r="79" spans="2:38">
-      <c r="B79" s="54"/>
+      <c r="B79" s="52"/>
       <c r="C79" s="33" t="s">
         <v>511</v>
       </c>
@@ -24267,7 +24311,7 @@
       </c>
     </row>
     <row r="80" spans="2:38">
-      <c r="B80" s="54"/>
+      <c r="B80" s="52"/>
       <c r="C80" s="4" t="s">
         <v>512</v>
       </c>
@@ -24335,7 +24379,7 @@
         <f t="shared" si="15"/>
         <v>0.16182995466847166</v>
       </c>
-      <c r="T80" s="55">
+      <c r="T80" s="53">
         <f t="shared" si="15"/>
         <v>9.2377307257793889E-2</v>
       </c>
@@ -24388,8 +24432,8 @@
         <v>1.3512487829864135</v>
       </c>
     </row>
-    <row r="81" spans="2:33">
-      <c r="B81" s="54"/>
+    <row r="81" spans="2:38">
+      <c r="B81" s="52"/>
       <c r="C81" s="23" t="s">
         <v>513</v>
       </c>
@@ -24442,84 +24486,132 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="82" spans="2:33">
-      <c r="B82" s="54"/>
+    <row r="82" spans="2:38">
+      <c r="B82" s="52"/>
       <c r="C82" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="83" spans="2:33">
-      <c r="B83" s="54"/>
+      <c r="H82" s="40">
+        <v>4.0000000000000008E-2</v>
+      </c>
+      <c r="I82" s="40">
+        <v>4.933333333333334E-2</v>
+      </c>
+      <c r="J82" s="40">
+        <v>5.8666666666666673E-2</v>
+      </c>
+      <c r="K82" s="40">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="L82" s="40">
+        <v>7.7333333333333337E-2</v>
+      </c>
+      <c r="M82" s="40">
+        <v>8.666666666666667E-2</v>
+      </c>
+      <c r="N82" s="40">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="O82" s="40">
+        <v>0.10533333333333333</v>
+      </c>
+      <c r="P82" s="40">
+        <v>0.11466666666666667</v>
+      </c>
+      <c r="Q82" s="40">
+        <v>0.124</v>
+      </c>
+      <c r="R82" s="40">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="S82" s="40">
+        <v>0.14266666666666666</v>
+      </c>
+      <c r="T82" s="40">
+        <v>0.152</v>
+      </c>
+      <c r="U82" s="40">
+        <v>0.16133333333333333</v>
+      </c>
+      <c r="V82" s="40">
+        <v>0.17066666666666666</v>
+      </c>
+      <c r="W82" s="40">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="83" spans="2:38">
+      <c r="B83" s="52"/>
       <c r="C83" s="34" t="s">
         <v>515</v>
       </c>
-      <c r="H83">
+      <c r="H83" s="55">
         <f>H81*H82</f>
-        <v>0</v>
-      </c>
-      <c r="I83">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="I83" s="55">
         <f>H83</f>
-        <v>0</v>
-      </c>
-      <c r="J83">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="J83" s="55">
         <f t="shared" ref="J83:K83" si="16">I83</f>
-        <v>0</v>
-      </c>
-      <c r="K83">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="K83" s="55">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="L83">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="L83" s="55">
         <f>L81*L82</f>
-        <v>0</v>
-      </c>
-      <c r="M83">
+        <v>1.541511111111111E-2</v>
+      </c>
+      <c r="M83" s="55">
         <f>L83</f>
-        <v>0</v>
-      </c>
-      <c r="N83">
+        <v>1.541511111111111E-2</v>
+      </c>
+      <c r="N83" s="55">
         <f t="shared" ref="N83:O83" si="17">M83</f>
-        <v>0</v>
-      </c>
-      <c r="O83">
+        <v>1.541511111111111E-2</v>
+      </c>
+      <c r="O83" s="55">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P83">
+        <v>1.541511111111111E-2</v>
+      </c>
+      <c r="P83" s="55">
         <f>P81*P82</f>
-        <v>0</v>
-      </c>
-      <c r="Q83">
+        <v>3.5393777777777774E-2</v>
+      </c>
+      <c r="Q83" s="55">
         <f>P83</f>
-        <v>0</v>
-      </c>
-      <c r="R83">
+        <v>3.5393777777777774E-2</v>
+      </c>
+      <c r="R83" s="55">
         <f t="shared" ref="R83:S83" si="18">Q83</f>
-        <v>0</v>
-      </c>
-      <c r="S83">
+        <v>3.5393777777777774E-2</v>
+      </c>
+      <c r="S83" s="55">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="T83">
+        <v>3.5393777777777774E-2</v>
+      </c>
+      <c r="T83" s="55">
         <f>T81*T82</f>
-        <v>0</v>
-      </c>
-      <c r="U83">
+        <v>6.3535999999999995E-2</v>
+      </c>
+      <c r="U83" s="55">
         <f>T83</f>
-        <v>0</v>
-      </c>
-      <c r="V83">
+        <v>6.3535999999999995E-2</v>
+      </c>
+      <c r="V83" s="55">
         <f t="shared" ref="V83:W83" si="19">U83</f>
-        <v>0</v>
-      </c>
-      <c r="W83">
+        <v>6.3535999999999995E-2</v>
+      </c>
+      <c r="W83" s="55">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="2:33">
-      <c r="B84" s="54" t="s">
+        <v>6.3535999999999995E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="2:38">
+      <c r="B84" s="52" t="s">
         <v>507</v>
       </c>
       <c r="C84" t="s">
@@ -24616,106 +24708,424 @@
         <v>39176000</v>
       </c>
     </row>
-    <row r="85" spans="2:33">
-      <c r="B85" s="54"/>
+    <row r="85" spans="2:38">
+      <c r="B85" s="52"/>
       <c r="C85" s="33" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="86" spans="2:33">
-      <c r="B86" s="54"/>
+      <c r="D85">
+        <v>38766720</v>
+      </c>
+      <c r="E85">
+        <v>48776720</v>
+      </c>
+      <c r="F85">
+        <v>48696720</v>
+      </c>
+      <c r="G85">
+        <v>48776720</v>
+      </c>
+      <c r="H85">
+        <v>47796720</v>
+      </c>
+      <c r="I85">
+        <v>46076720</v>
+      </c>
+      <c r="J85">
+        <v>48696720</v>
+      </c>
+      <c r="K85">
+        <v>48776720</v>
+      </c>
+      <c r="L85">
+        <v>45216720</v>
+      </c>
+      <c r="M85">
+        <v>47876720</v>
+      </c>
+      <c r="N85">
+        <v>43836720</v>
+      </c>
+      <c r="O85">
+        <v>48676720</v>
+      </c>
+      <c r="P85">
+        <v>48696720</v>
+      </c>
+      <c r="Q85">
+        <v>48776720</v>
+      </c>
+      <c r="R85">
+        <v>47796720</v>
+      </c>
+      <c r="S85">
+        <v>46176720</v>
+      </c>
+      <c r="T85">
+        <v>45216720</v>
+      </c>
+      <c r="U85">
+        <v>48676720</v>
+      </c>
+      <c r="V85">
+        <v>46436720</v>
+      </c>
+      <c r="W85">
+        <v>47876720</v>
+      </c>
+      <c r="X85">
+        <v>46096720</v>
+      </c>
+      <c r="Y85">
+        <v>48776720</v>
+      </c>
+      <c r="Z85">
+        <v>48696720</v>
+      </c>
+      <c r="AA85">
+        <v>48676720</v>
+      </c>
+      <c r="AB85">
+        <v>44316720</v>
+      </c>
+      <c r="AC85">
+        <v>46176720</v>
+      </c>
+      <c r="AD85">
+        <v>48696720</v>
+      </c>
+      <c r="AE85">
+        <v>48776720</v>
+      </c>
+      <c r="AF85">
+        <v>48696720</v>
+      </c>
+      <c r="AG85">
+        <v>47776720</v>
+      </c>
+    </row>
+    <row r="86" spans="2:38">
+      <c r="B86" s="52"/>
       <c r="C86" s="4" t="s">
         <v>512</v>
       </c>
       <c r="D86" s="20">
         <f>(D85-D84)/D84</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="87" spans="2:33">
-      <c r="B87" s="54"/>
+        <v>-6.3062645011600929E-2</v>
+      </c>
+      <c r="E86" s="20">
+        <f t="shared" ref="E86:AG86" si="20">(E85-E84)/E84</f>
+        <v>0.21710549955085337</v>
+      </c>
+      <c r="F86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.21753975397539754</v>
+      </c>
+      <c r="G86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.21710549955085337</v>
+      </c>
+      <c r="H86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.22254757519950891</v>
+      </c>
+      <c r="I86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.14973350633795787</v>
+      </c>
+      <c r="J86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.21753975397539754</v>
+      </c>
+      <c r="K86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.21710549955085337</v>
+      </c>
+      <c r="L86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.13053105310531052</v>
+      </c>
+      <c r="M86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.22209311823565447</v>
+      </c>
+      <c r="N86" s="20">
+        <f t="shared" si="20"/>
+        <v>9.6027602760276026E-2</v>
+      </c>
+      <c r="O86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.21461024054296837</v>
+      </c>
+      <c r="P86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.21753975397539754</v>
+      </c>
+      <c r="Q86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.21710549955085337</v>
+      </c>
+      <c r="R86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.22254757519950891</v>
+      </c>
+      <c r="S86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.1522287653458429</v>
+      </c>
+      <c r="T86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.13053105310531052</v>
+      </c>
+      <c r="U86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.21461024054296837</v>
+      </c>
+      <c r="V86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.16103410341034102</v>
+      </c>
+      <c r="W86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.22209311823565447</v>
+      </c>
+      <c r="X86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.15253325332533255</v>
+      </c>
+      <c r="Y86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.21710549955085337</v>
+      </c>
+      <c r="Z86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.21753975397539754</v>
+      </c>
+      <c r="AA86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.21461024054296837</v>
+      </c>
+      <c r="AB86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.13353591160220996</v>
+      </c>
+      <c r="AC86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.1522287653458429</v>
+      </c>
+      <c r="AD86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.21753975397539754</v>
+      </c>
+      <c r="AE86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.21710549955085337</v>
+      </c>
+      <c r="AF86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.21753975397539754</v>
+      </c>
+      <c r="AG86" s="20">
+        <f t="shared" si="20"/>
+        <v>0.21954053502144169</v>
+      </c>
+      <c r="AI86" s="20" cm="1">
+        <f t="array" ref="AI86">MEDIAN(_xlfn._xlws.FILTER(D86:AG86, D86:AG86 &lt;= _xlfn.QUARTILE.INC(D86:AG86, 1)))</f>
+        <v>0.13203348235376022</v>
+      </c>
+      <c r="AJ86" s="20" cm="1">
+        <f t="array" ref="AJ86">MEDIAN(_xlfn._xlws.FILTER(D86:AG86, (D86:AG86 &gt; _xlfn.QUARTILE.INC(D86:AG86, 1)) * (D86:AG86 &lt;= _xlfn.QUARTILE.INC(D86:AG86, 2))))</f>
+        <v>0.21710549955085337</v>
+      </c>
+      <c r="AK86" s="20" cm="1">
+        <f t="array" ref="AK86">MEDIAN(_xlfn._xlws.FILTER(D86:AG86, (D86:AG86 &gt; _xlfn.QUARTILE.INC(D86:AG86, 2)) * (D86:AG86 &lt;= _xlfn.QUARTILE.INC(D86:AG86, 3))))</f>
+        <v>0.21753975397539754</v>
+      </c>
+      <c r="AL86" s="20" cm="1">
+        <f t="array" ref="AL86">MEDIAN(_xlfn._xlws.FILTER(D86:AG86, D86:AG86 &gt; _xlfn.QUARTILE.INC(D86:AG86, 3)))</f>
+        <v>0.22209311823565447</v>
+      </c>
+    </row>
+    <row r="87" spans="2:38">
+      <c r="B87" s="52"/>
       <c r="C87" s="23" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="88" spans="2:33">
-      <c r="B88" s="54"/>
+      <c r="H87" s="40">
+        <v>0.13000000000000003</v>
+      </c>
+      <c r="I87" s="40">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="J87" s="40">
+        <v>0.14200000000000002</v>
+      </c>
+      <c r="K87" s="40">
+        <v>0.14800000000000002</v>
+      </c>
+      <c r="L87" s="40">
+        <v>0.15400000000000003</v>
+      </c>
+      <c r="M87" s="40">
+        <v>0.16</v>
+      </c>
+      <c r="N87" s="40">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="O87" s="40">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="P87" s="40">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="Q87" s="40">
+        <v>0.184</v>
+      </c>
+      <c r="R87" s="40">
+        <v>0.19</v>
+      </c>
+      <c r="S87" s="40">
+        <v>0.19599999999999998</v>
+      </c>
+      <c r="T87" s="40">
+        <v>0.20199999999999999</v>
+      </c>
+      <c r="U87" s="40">
+        <v>0.20799999999999996</v>
+      </c>
+      <c r="V87" s="40">
+        <v>0.21399999999999997</v>
+      </c>
+      <c r="W87" s="40">
+        <v>0.21999999999999997</v>
+      </c>
+    </row>
+    <row r="88" spans="2:38">
+      <c r="B88" s="52"/>
       <c r="C88" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="89" spans="2:33">
-      <c r="B89" s="54"/>
+      <c r="H88" s="40">
+        <v>4.0000000000000008E-2</v>
+      </c>
+      <c r="I88" s="40">
+        <v>4.933333333333334E-2</v>
+      </c>
+      <c r="J88" s="40">
+        <v>5.8666666666666673E-2</v>
+      </c>
+      <c r="K88" s="40">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="L88" s="40">
+        <v>7.7333333333333337E-2</v>
+      </c>
+      <c r="M88" s="40">
+        <v>8.666666666666667E-2</v>
+      </c>
+      <c r="N88" s="40">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="O88" s="40">
+        <v>0.10533333333333333</v>
+      </c>
+      <c r="P88" s="40">
+        <v>0.11466666666666667</v>
+      </c>
+      <c r="Q88" s="40">
+        <v>0.124</v>
+      </c>
+      <c r="R88" s="40">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="S88" s="40">
+        <v>0.14266666666666666</v>
+      </c>
+      <c r="T88" s="40">
+        <v>0.152</v>
+      </c>
+      <c r="U88" s="40">
+        <v>0.16133333333333333</v>
+      </c>
+      <c r="V88" s="40">
+        <v>0.17066666666666666</v>
+      </c>
+      <c r="W88" s="40">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="89" spans="2:38">
+      <c r="B89" s="52"/>
       <c r="C89" s="34" t="s">
         <v>515</v>
       </c>
-      <c r="H89">
+      <c r="H89" s="55">
         <f>H87*H88</f>
-        <v>0</v>
-      </c>
-      <c r="I89">
+        <v>5.2000000000000024E-3</v>
+      </c>
+      <c r="I89" s="55">
         <f>H89</f>
-        <v>0</v>
-      </c>
-      <c r="J89">
-        <f t="shared" ref="J89:K89" si="20">I89</f>
-        <v>0</v>
-      </c>
-      <c r="K89">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="L89">
+        <v>5.2000000000000024E-3</v>
+      </c>
+      <c r="J89" s="55">
+        <f t="shared" ref="J89:K89" si="21">I89</f>
+        <v>5.2000000000000024E-3</v>
+      </c>
+      <c r="K89" s="55">
+        <f t="shared" si="21"/>
+        <v>5.2000000000000024E-3</v>
+      </c>
+      <c r="L89" s="55">
         <f>L87*L88</f>
-        <v>0</v>
-      </c>
-      <c r="M89">
+        <v>1.1909333333333336E-2</v>
+      </c>
+      <c r="M89" s="55">
         <f>L89</f>
-        <v>0</v>
-      </c>
-      <c r="N89">
-        <f t="shared" ref="N89:O89" si="21">M89</f>
-        <v>0</v>
-      </c>
-      <c r="O89">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P89">
+        <v>1.1909333333333336E-2</v>
+      </c>
+      <c r="N89" s="55">
+        <f t="shared" ref="N89:O89" si="22">M89</f>
+        <v>1.1909333333333336E-2</v>
+      </c>
+      <c r="O89" s="55">
+        <f t="shared" si="22"/>
+        <v>1.1909333333333336E-2</v>
+      </c>
+      <c r="P89" s="55">
         <f>P87*P88</f>
-        <v>0</v>
-      </c>
-      <c r="Q89">
+        <v>2.0410666666666667E-2</v>
+      </c>
+      <c r="Q89" s="55">
         <f>P89</f>
-        <v>0</v>
-      </c>
-      <c r="R89">
-        <f t="shared" ref="R89:S89" si="22">Q89</f>
-        <v>0</v>
-      </c>
-      <c r="S89">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="T89">
+        <v>2.0410666666666667E-2</v>
+      </c>
+      <c r="R89" s="55">
+        <f t="shared" ref="R89:S89" si="23">Q89</f>
+        <v>2.0410666666666667E-2</v>
+      </c>
+      <c r="S89" s="55">
+        <f t="shared" si="23"/>
+        <v>2.0410666666666667E-2</v>
+      </c>
+      <c r="T89" s="55">
         <f>T87*T88</f>
-        <v>0</v>
-      </c>
-      <c r="U89">
+        <v>3.0703999999999999E-2</v>
+      </c>
+      <c r="U89" s="55">
         <f>T89</f>
-        <v>0</v>
-      </c>
-      <c r="V89">
-        <f t="shared" ref="V89:W89" si="23">U89</f>
-        <v>0</v>
-      </c>
-      <c r="W89">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="2:33">
-      <c r="B90" s="54" t="s">
+        <v>3.0703999999999999E-2</v>
+      </c>
+      <c r="V89" s="55">
+        <f t="shared" ref="V89:W89" si="24">U89</f>
+        <v>3.0703999999999999E-2</v>
+      </c>
+      <c r="W89" s="55">
+        <f t="shared" si="24"/>
+        <v>3.0703999999999999E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="2:38">
+      <c r="B90" s="52" t="s">
         <v>508</v>
       </c>
       <c r="C90" t="s">
@@ -24812,106 +25222,424 @@
         <v>25105400</v>
       </c>
     </row>
-    <row r="91" spans="2:33">
-      <c r="B91" s="54"/>
+    <row r="91" spans="2:38">
+      <c r="B91" s="52"/>
       <c r="C91" s="33" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="92" spans="2:33">
-      <c r="B92" s="54"/>
+      <c r="D91">
+        <v>25625970</v>
+      </c>
+      <c r="E91">
+        <v>26845970</v>
+      </c>
+      <c r="F91">
+        <v>26525970</v>
+      </c>
+      <c r="G91">
+        <v>26845970</v>
+      </c>
+      <c r="H91">
+        <v>26525970</v>
+      </c>
+      <c r="I91">
+        <v>25945970</v>
+      </c>
+      <c r="J91">
+        <v>26525970</v>
+      </c>
+      <c r="K91">
+        <v>26845970</v>
+      </c>
+      <c r="L91">
+        <v>26525970</v>
+      </c>
+      <c r="M91">
+        <v>26845970</v>
+      </c>
+      <c r="N91">
+        <v>25625970</v>
+      </c>
+      <c r="O91">
+        <v>26845970</v>
+      </c>
+      <c r="P91">
+        <v>26525970</v>
+      </c>
+      <c r="Q91">
+        <v>26845970</v>
+      </c>
+      <c r="R91">
+        <v>26525970</v>
+      </c>
+      <c r="S91">
+        <v>25945970</v>
+      </c>
+      <c r="T91">
+        <v>26525970</v>
+      </c>
+      <c r="U91">
+        <v>26845970</v>
+      </c>
+      <c r="V91">
+        <v>26525970</v>
+      </c>
+      <c r="W91">
+        <v>26845970</v>
+      </c>
+      <c r="X91">
+        <v>25625970</v>
+      </c>
+      <c r="Y91">
+        <v>26845970</v>
+      </c>
+      <c r="Z91">
+        <v>26525970</v>
+      </c>
+      <c r="AA91">
+        <v>26845970</v>
+      </c>
+      <c r="AB91">
+        <v>26525970</v>
+      </c>
+      <c r="AC91">
+        <v>26395970</v>
+      </c>
+      <c r="AD91">
+        <v>26525970</v>
+      </c>
+      <c r="AE91">
+        <v>26845970</v>
+      </c>
+      <c r="AF91">
+        <v>26525970</v>
+      </c>
+      <c r="AG91">
+        <v>26845970</v>
+      </c>
+    </row>
+    <row r="92" spans="2:38">
+      <c r="B92" s="52"/>
       <c r="C92" s="4" t="s">
         <v>512</v>
       </c>
       <c r="D92" s="20">
         <f>(D91-D90)/D90</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="93" spans="2:33">
-      <c r="B93" s="54"/>
+        <v>7.2871712426838153E-2</v>
+      </c>
+      <c r="E92" s="20">
+        <f t="shared" ref="E92:AG92" si="25">(E91-E90)/E90</f>
+        <v>6.9330502601034044E-2</v>
+      </c>
+      <c r="F92" s="20">
+        <f t="shared" si="25"/>
+        <v>7.0225616693698714E-2</v>
+      </c>
+      <c r="G92" s="20">
+        <f t="shared" si="25"/>
+        <v>6.9330502601034044E-2</v>
+      </c>
+      <c r="H92" s="20">
+        <f t="shared" si="25"/>
+        <v>7.0225616693698714E-2</v>
+      </c>
+      <c r="I92" s="20">
+        <f t="shared" si="25"/>
+        <v>7.1908334503871033E-2</v>
+      </c>
+      <c r="J92" s="20">
+        <f t="shared" si="25"/>
+        <v>7.0225616693698714E-2</v>
+      </c>
+      <c r="K92" s="20">
+        <f t="shared" si="25"/>
+        <v>6.9330502601034044E-2</v>
+      </c>
+      <c r="L92" s="20">
+        <f t="shared" si="25"/>
+        <v>7.0225616693698714E-2</v>
+      </c>
+      <c r="M92" s="20">
+        <f t="shared" si="25"/>
+        <v>6.9330502601034044E-2</v>
+      </c>
+      <c r="N92" s="20">
+        <f t="shared" si="25"/>
+        <v>7.2871712426838153E-2</v>
+      </c>
+      <c r="O92" s="20">
+        <f t="shared" si="25"/>
+        <v>6.9330502601034044E-2</v>
+      </c>
+      <c r="P92" s="20">
+        <f t="shared" si="25"/>
+        <v>7.0225616693698714E-2</v>
+      </c>
+      <c r="Q92" s="20">
+        <f t="shared" si="25"/>
+        <v>6.9330502601034044E-2</v>
+      </c>
+      <c r="R92" s="20">
+        <f t="shared" si="25"/>
+        <v>7.0225616693698714E-2</v>
+      </c>
+      <c r="S92" s="20">
+        <f t="shared" si="25"/>
+        <v>7.1908334503871033E-2</v>
+      </c>
+      <c r="T92" s="20">
+        <f t="shared" si="25"/>
+        <v>7.0225616693698714E-2</v>
+      </c>
+      <c r="U92" s="20">
+        <f t="shared" si="25"/>
+        <v>6.9330502601034044E-2</v>
+      </c>
+      <c r="V92" s="20">
+        <f t="shared" si="25"/>
+        <v>7.0225616693698714E-2</v>
+      </c>
+      <c r="W92" s="20">
+        <f t="shared" si="25"/>
+        <v>6.9330502601034044E-2</v>
+      </c>
+      <c r="X92" s="20">
+        <f t="shared" si="25"/>
+        <v>7.2871712426838153E-2</v>
+      </c>
+      <c r="Y92" s="20">
+        <f t="shared" si="25"/>
+        <v>6.9330502601034044E-2</v>
+      </c>
+      <c r="Z92" s="20">
+        <f t="shared" si="25"/>
+        <v>7.0225616693698714E-2</v>
+      </c>
+      <c r="AA92" s="20">
+        <f t="shared" si="25"/>
+        <v>6.9330502601034044E-2</v>
+      </c>
+      <c r="AB92" s="20">
+        <f t="shared" si="25"/>
+        <v>7.0225616693698714E-2</v>
+      </c>
+      <c r="AC92" s="20">
+        <f t="shared" si="25"/>
+        <v>7.0595893800141141E-2</v>
+      </c>
+      <c r="AD92" s="20">
+        <f t="shared" si="25"/>
+        <v>7.0225616693698714E-2</v>
+      </c>
+      <c r="AE92" s="20">
+        <f t="shared" si="25"/>
+        <v>6.9330502601034044E-2</v>
+      </c>
+      <c r="AF92" s="20">
+        <f t="shared" si="25"/>
+        <v>7.0225616693698714E-2</v>
+      </c>
+      <c r="AG92" s="20">
+        <f t="shared" si="25"/>
+        <v>6.9330502601034044E-2</v>
+      </c>
+      <c r="AI92" s="20" cm="1">
+        <f t="array" ref="AI92">MEDIAN(_xlfn._xlws.FILTER(D92:AG92, D92:AG92 &lt;= _xlfn.QUARTILE.INC(D92:AG92, 1)))</f>
+        <v>6.9330502601034044E-2</v>
+      </c>
+      <c r="AJ92" s="20" cm="1">
+        <f t="array" ref="AJ92">MEDIAN(_xlfn._xlws.FILTER(D92:AG92, (D92:AG92 &gt; _xlfn.QUARTILE.INC(D92:AG92, 1)) * (D92:AG92 &lt;= _xlfn.QUARTILE.INC(D92:AG92, 2))))</f>
+        <v>7.0225616693698714E-2</v>
+      </c>
+      <c r="AK92" s="20" t="e" cm="1" vm="1">
+        <f t="array" ref="AK92">MEDIAN(_xlfn._xlws.FILTER(D92:AG92, (D92:AG92 &gt; _xlfn.QUARTILE.INC(D92:AG92, 2)) * (D92:AG92 &lt;= _xlfn.QUARTILE.INC(D92:AG92, 3))))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AL92" s="20" cm="1">
+        <f t="array" ref="AL92">MEDIAN(_xlfn._xlws.FILTER(D92:AG92, D92:AG92 &gt; _xlfn.QUARTILE.INC(D92:AG92, 3)))</f>
+        <v>7.2390023465354586E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="2:38">
+      <c r="B93" s="52"/>
       <c r="C93" s="23" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="94" spans="2:33">
-      <c r="B94" s="54"/>
+      <c r="H93" s="40">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I93" s="40">
+        <v>7.2000000000000008E-2</v>
+      </c>
+      <c r="J93" s="40">
+        <v>7.400000000000001E-2</v>
+      </c>
+      <c r="K93" s="40">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="L93" s="40">
+        <v>7.8E-2</v>
+      </c>
+      <c r="M93" s="40">
+        <v>0.08</v>
+      </c>
+      <c r="N93" s="40">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="O93" s="40">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="P93" s="40">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="Q93" s="40">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="R93" s="40">
+        <v>0.09</v>
+      </c>
+      <c r="S93" s="40">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="T93" s="40">
+        <v>9.4E-2</v>
+      </c>
+      <c r="U93" s="40">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="V93" s="40">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="W93" s="40">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="94" spans="2:38">
+      <c r="B94" s="52"/>
       <c r="C94" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="95" spans="2:33">
-      <c r="B95" s="54"/>
+      <c r="H94" s="56">
+        <v>4.0000000000000008E-2</v>
+      </c>
+      <c r="I94" s="56">
+        <v>4.933333333333334E-2</v>
+      </c>
+      <c r="J94" s="56">
+        <v>5.8666666666666673E-2</v>
+      </c>
+      <c r="K94" s="56">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="L94" s="56">
+        <v>7.7333333333333337E-2</v>
+      </c>
+      <c r="M94" s="56">
+        <v>8.666666666666667E-2</v>
+      </c>
+      <c r="N94" s="56">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="O94" s="56">
+        <v>0.10533333333333333</v>
+      </c>
+      <c r="P94" s="56">
+        <v>0.11466666666666667</v>
+      </c>
+      <c r="Q94" s="56">
+        <v>0.124</v>
+      </c>
+      <c r="R94" s="56">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="S94" s="56">
+        <v>0.14266666666666666</v>
+      </c>
+      <c r="T94" s="56">
+        <v>0.152</v>
+      </c>
+      <c r="U94" s="56">
+        <v>0.16133333333333333</v>
+      </c>
+      <c r="V94" s="56">
+        <v>0.17066666666666666</v>
+      </c>
+      <c r="W94" s="56">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="95" spans="2:38">
+      <c r="B95" s="52"/>
       <c r="C95" s="34" t="s">
         <v>515</v>
       </c>
       <c r="H95">
         <f>H93*H94</f>
-        <v>0</v>
+        <v>2.8000000000000008E-3</v>
       </c>
       <c r="I95">
         <f>H95</f>
-        <v>0</v>
+        <v>2.8000000000000008E-3</v>
       </c>
       <c r="J95">
-        <f t="shared" ref="J95:K95" si="24">I95</f>
-        <v>0</v>
+        <f t="shared" ref="J95:K95" si="26">I95</f>
+        <v>2.8000000000000008E-3</v>
       </c>
       <c r="K95">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f t="shared" si="26"/>
+        <v>2.8000000000000008E-3</v>
       </c>
       <c r="L95">
         <f>L93*L94</f>
-        <v>0</v>
+        <v>6.032E-3</v>
       </c>
       <c r="M95">
         <f>L95</f>
-        <v>0</v>
+        <v>6.032E-3</v>
       </c>
       <c r="N95">
-        <f t="shared" ref="N95:O95" si="25">M95</f>
-        <v>0</v>
+        <f t="shared" ref="N95:O95" si="27">M95</f>
+        <v>6.032E-3</v>
       </c>
       <c r="O95">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f t="shared" si="27"/>
+        <v>6.032E-3</v>
       </c>
       <c r="P95">
         <f>P93*P94</f>
-        <v>0</v>
+        <v>9.8613333333333331E-3</v>
       </c>
       <c r="Q95">
         <f>P95</f>
-        <v>0</v>
+        <v>9.8613333333333331E-3</v>
       </c>
       <c r="R95">
-        <f t="shared" ref="R95:S95" si="26">Q95</f>
-        <v>0</v>
+        <f t="shared" ref="R95:S95" si="28">Q95</f>
+        <v>9.8613333333333331E-3</v>
       </c>
       <c r="S95">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="28"/>
+        <v>9.8613333333333331E-3</v>
       </c>
       <c r="T95">
         <f>T93*T94</f>
-        <v>0</v>
+        <v>1.4288E-2</v>
       </c>
       <c r="U95">
         <f>T95</f>
-        <v>0</v>
+        <v>1.4288E-2</v>
       </c>
       <c r="V95">
-        <f t="shared" ref="V95:W95" si="27">U95</f>
-        <v>0</v>
+        <f t="shared" ref="V95:W95" si="29">U95</f>
+        <v>1.4288E-2</v>
       </c>
       <c r="W95">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="2:33">
-      <c r="B96" s="54" t="s">
+        <f t="shared" si="29"/>
+        <v>1.4288E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="2:38">
+      <c r="B96" s="52" t="s">
         <v>509</v>
       </c>
       <c r="C96" t="s">
@@ -24949,7 +25677,7 @@
       </c>
     </row>
     <row r="97" spans="2:38">
-      <c r="B97" s="54"/>
+      <c r="B97" s="52"/>
       <c r="C97" s="33" t="s">
         <v>511</v>
       </c>
@@ -24985,48 +25713,48 @@
       </c>
     </row>
     <row r="98" spans="2:38">
-      <c r="B98" s="54"/>
+      <c r="B98" s="52"/>
       <c r="C98" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="D98" s="55">
+      <c r="D98" s="53">
         <f>(D97-D96)/D96</f>
         <v>7.8251188171096553E-2</v>
       </c>
-      <c r="E98" s="55">
-        <f t="shared" ref="E98:M98" si="28">(E97-E96)/E96</f>
+      <c r="E98" s="53">
+        <f t="shared" ref="E98:M98" si="30">(E97-E96)/E96</f>
         <v>0.25095732520480085</v>
       </c>
       <c r="F98" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.17251970774850994</v>
       </c>
       <c r="G98" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.15909577574459807</v>
       </c>
       <c r="H98" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.17251970774851003</v>
       </c>
       <c r="I98" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>-0.51170533642691418</v>
       </c>
       <c r="J98" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>7.8065435252505422E-2</v>
       </c>
       <c r="K98" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.25095732520480096</v>
       </c>
       <c r="L98" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.17251970774850989</v>
       </c>
       <c r="M98" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.15909577574459818</v>
       </c>
       <c r="AI98" s="20" cm="1">
@@ -25047,7 +25775,7 @@
       </c>
     </row>
     <row r="99" spans="2:38">
-      <c r="B99" s="54"/>
+      <c r="B99" s="52"/>
       <c r="C99" s="23" t="s">
         <v>513</v>
       </c>
@@ -25071,80 +25799,481 @@
       </c>
     </row>
     <row r="100" spans="2:38">
-      <c r="B100" s="54"/>
+      <c r="B100" s="52"/>
       <c r="C100" t="s">
         <v>514</v>
       </c>
+      <c r="H100" s="40">
+        <v>4.0000000000000008E-2</v>
+      </c>
+      <c r="I100" s="40">
+        <v>4.933333333333334E-2</v>
+      </c>
+      <c r="J100" s="40">
+        <v>5.8666666666666673E-2</v>
+      </c>
+      <c r="K100" s="40">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="L100" s="40">
+        <v>7.7333333333333337E-2</v>
+      </c>
+      <c r="M100" s="40">
+        <v>8.666666666666667E-2</v>
+      </c>
+      <c r="N100" s="40"/>
+      <c r="O100" s="40"/>
+      <c r="P100" s="40"/>
+      <c r="Q100" s="40"/>
+      <c r="R100" s="40"/>
+      <c r="S100" s="40"/>
+      <c r="T100" s="40"/>
+      <c r="U100" s="40"/>
+      <c r="V100" s="40"/>
+      <c r="W100" s="40"/>
     </row>
     <row r="101" spans="2:38">
-      <c r="B101" s="54"/>
+      <c r="B101" s="52"/>
       <c r="C101" s="34" t="s">
         <v>515</v>
       </c>
-      <c r="H101">
-        <f>H99*H100</f>
-        <v>0</v>
-      </c>
-      <c r="I101">
+      <c r="H101" s="55">
+        <v>3.2000000000000015E-3</v>
+      </c>
+      <c r="I101" s="55">
+        <v>4.100266666666668E-3</v>
+      </c>
+      <c r="J101" s="55">
+        <v>5.0005333333333355E-3</v>
+      </c>
+      <c r="K101" s="55">
+        <v>5.9008000000000021E-3</v>
+      </c>
+      <c r="L101" s="55">
+        <v>6.8010666666666686E-3</v>
+      </c>
+      <c r="M101" s="55">
+        <v>7.7013333333333361E-3</v>
+      </c>
+      <c r="N101" s="55">
+        <v>8.6016000000000026E-3</v>
+      </c>
+      <c r="O101" s="55">
+        <v>9.5018666666666692E-3</v>
+      </c>
+      <c r="P101" s="55">
+        <v>1.0402133333333336E-2</v>
+      </c>
+      <c r="Q101" s="55">
+        <v>1.1302400000000002E-2</v>
+      </c>
+      <c r="R101" s="55">
+        <v>1.2202666666666669E-2</v>
+      </c>
+      <c r="S101" s="55">
+        <v>1.3102933333333337E-2</v>
+      </c>
+      <c r="T101" s="55">
+        <v>1.4003200000000004E-2</v>
+      </c>
+      <c r="U101" s="55">
+        <v>1.490346666666667E-2</v>
+      </c>
+      <c r="V101" s="55">
+        <v>1.5803733333333337E-2</v>
+      </c>
+      <c r="W101" s="55">
+        <v>1.6704000000000004E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="2:38">
+      <c r="B105" s="52" t="str">
+        <f>B2</f>
+        <v>Pertanian Tanaman Pangan</v>
+      </c>
+      <c r="H105" s="56">
+        <f>AVERAGE(H95,H89)</f>
+        <v>4.0000000000000018E-3</v>
+      </c>
+      <c r="I105" s="56">
+        <f t="shared" ref="I105:W105" si="31">AVERAGE(I95,I89)</f>
+        <v>4.0000000000000018E-3</v>
+      </c>
+      <c r="J105" s="56">
+        <f t="shared" si="31"/>
+        <v>4.0000000000000018E-3</v>
+      </c>
+      <c r="K105" s="56">
+        <f t="shared" si="31"/>
+        <v>4.0000000000000018E-3</v>
+      </c>
+      <c r="L105" s="56">
+        <f t="shared" si="31"/>
+        <v>8.9706666666666685E-3</v>
+      </c>
+      <c r="M105" s="56">
+        <f t="shared" si="31"/>
+        <v>8.9706666666666685E-3</v>
+      </c>
+      <c r="N105" s="56">
+        <f t="shared" si="31"/>
+        <v>8.9706666666666685E-3</v>
+      </c>
+      <c r="O105" s="56">
+        <f t="shared" si="31"/>
+        <v>8.9706666666666685E-3</v>
+      </c>
+      <c r="P105" s="56">
+        <f t="shared" si="31"/>
+        <v>1.5136E-2</v>
+      </c>
+      <c r="Q105" s="56">
+        <f t="shared" si="31"/>
+        <v>1.5136E-2</v>
+      </c>
+      <c r="R105" s="56">
+        <f t="shared" si="31"/>
+        <v>1.5136E-2</v>
+      </c>
+      <c r="S105" s="56">
+        <f t="shared" si="31"/>
+        <v>1.5136E-2</v>
+      </c>
+      <c r="T105" s="56">
+        <f t="shared" si="31"/>
+        <v>2.2495999999999999E-2</v>
+      </c>
+      <c r="U105" s="56">
+        <f t="shared" si="31"/>
+        <v>2.2495999999999999E-2</v>
+      </c>
+      <c r="V105" s="56">
+        <f t="shared" si="31"/>
+        <v>2.2495999999999999E-2</v>
+      </c>
+      <c r="W105" s="56">
+        <f t="shared" si="31"/>
+        <v>2.2495999999999999E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="2:38">
+      <c r="B106" s="59" t="str">
+        <f t="shared" ref="B106:B118" si="32">B3</f>
+        <v>Pertanian Tanaman Hortikultura Semusim, Hortikultura Tahunan, dan Lainnya</v>
+      </c>
+    </row>
+    <row r="107" spans="2:38">
+      <c r="B107" s="52" t="str">
+        <f t="shared" si="32"/>
+        <v>Karet</v>
+      </c>
+      <c r="H107" s="56">
+        <f>AVERAGE(H71,H77)</f>
+        <v>2.5500000000000028E-3</v>
+      </c>
+      <c r="I107" s="56">
+        <f t="shared" ref="I107:W107" si="33">AVERAGE(I71,I77)</f>
+        <v>2.5500000000000028E-3</v>
+      </c>
+      <c r="J107" s="56">
+        <f t="shared" si="33"/>
+        <v>2.5500000000000028E-3</v>
+      </c>
+      <c r="K107" s="56">
+        <f t="shared" si="33"/>
+        <v>2.5500000000000028E-3</v>
+      </c>
+      <c r="L107" s="56">
+        <f t="shared" si="33"/>
+        <v>1.2169555555555558E-2</v>
+      </c>
+      <c r="M107" s="56">
+        <f t="shared" si="33"/>
+        <v>1.2169555555555558E-2</v>
+      </c>
+      <c r="N107" s="56">
+        <f t="shared" si="33"/>
+        <v>1.2169555555555558E-2</v>
+      </c>
+      <c r="O107" s="56">
+        <f t="shared" si="33"/>
+        <v>1.2169555555555558E-2</v>
+      </c>
+      <c r="P107" s="56">
+        <f t="shared" si="33"/>
+        <v>2.8814888888888886E-2</v>
+      </c>
+      <c r="Q107" s="56">
+        <f t="shared" si="33"/>
+        <v>2.8814888888888886E-2</v>
+      </c>
+      <c r="R107" s="56">
+        <f t="shared" si="33"/>
+        <v>2.8814888888888886E-2</v>
+      </c>
+      <c r="S107" s="56">
+        <f t="shared" si="33"/>
+        <v>2.8814888888888886E-2</v>
+      </c>
+      <c r="T107" s="56">
+        <f t="shared" si="33"/>
+        <v>5.2485999999999998E-2</v>
+      </c>
+      <c r="U107" s="56">
+        <f t="shared" si="33"/>
+        <v>5.2485999999999998E-2</v>
+      </c>
+      <c r="V107" s="56">
+        <f t="shared" si="33"/>
+        <v>5.2485999999999998E-2</v>
+      </c>
+      <c r="W107" s="56">
+        <f t="shared" si="33"/>
+        <v>5.2485999999999998E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="2:38">
+      <c r="B108" s="52" t="str">
+        <f t="shared" si="32"/>
+        <v>Kelapa Sawit</v>
+      </c>
+      <c r="H108" s="56">
+        <f>H83</f>
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="I108" s="56">
+        <f t="shared" ref="I108:W108" si="34">I83</f>
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="J108" s="56">
+        <f t="shared" si="34"/>
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="K108" s="56">
+        <f t="shared" si="34"/>
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="L108" s="56">
+        <f t="shared" si="34"/>
+        <v>1.541511111111111E-2</v>
+      </c>
+      <c r="M108" s="56">
+        <f t="shared" si="34"/>
+        <v>1.541511111111111E-2</v>
+      </c>
+      <c r="N108" s="56">
+        <f t="shared" si="34"/>
+        <v>1.541511111111111E-2</v>
+      </c>
+      <c r="O108" s="56">
+        <f t="shared" si="34"/>
+        <v>1.541511111111111E-2</v>
+      </c>
+      <c r="P108" s="56">
+        <f t="shared" si="34"/>
+        <v>3.5393777777777774E-2</v>
+      </c>
+      <c r="Q108" s="56">
+        <f t="shared" si="34"/>
+        <v>3.5393777777777774E-2</v>
+      </c>
+      <c r="R108" s="56">
+        <f t="shared" si="34"/>
+        <v>3.5393777777777774E-2</v>
+      </c>
+      <c r="S108" s="56">
+        <f t="shared" si="34"/>
+        <v>3.5393777777777774E-2</v>
+      </c>
+      <c r="T108" s="56">
+        <f t="shared" si="34"/>
+        <v>6.3535999999999995E-2</v>
+      </c>
+      <c r="U108" s="56">
+        <f t="shared" si="34"/>
+        <v>6.3535999999999995E-2</v>
+      </c>
+      <c r="V108" s="56">
+        <f t="shared" si="34"/>
+        <v>6.3535999999999995E-2</v>
+      </c>
+      <c r="W108" s="56">
+        <f t="shared" si="34"/>
+        <v>6.3535999999999995E-2</v>
+      </c>
+    </row>
+    <row r="109" spans="2:38">
+      <c r="B109" s="52" t="str">
+        <f t="shared" si="32"/>
+        <v>Tanaman Perkebunan lainnya</v>
+      </c>
+      <c r="H109" s="56">
+        <f>H65</f>
+        <v>3.9809533183954061E-3</v>
+      </c>
+      <c r="I109" s="56">
+        <f t="shared" ref="I109:W109" si="35">I65</f>
+        <v>3.9809533183954061E-3</v>
+      </c>
+      <c r="J109" s="56">
+        <f t="shared" si="35"/>
+        <v>3.9809533183954061E-3</v>
+      </c>
+      <c r="K109" s="56">
+        <f t="shared" si="35"/>
+        <v>3.9809533183954061E-3</v>
+      </c>
+      <c r="L109" s="56">
+        <f t="shared" si="35"/>
+        <v>1.5780792698487447E-2</v>
+      </c>
+      <c r="M109" s="56">
+        <f t="shared" si="35"/>
+        <v>1.5780792698487447E-2</v>
+      </c>
+      <c r="N109" s="56">
+        <f t="shared" si="35"/>
+        <v>1.5780792698487447E-2</v>
+      </c>
+      <c r="O109" s="56">
+        <f t="shared" si="35"/>
+        <v>1.5780792698487447E-2</v>
+      </c>
+      <c r="P109" s="56">
+        <f t="shared" si="35"/>
+        <v>3.4983230673732831E-2</v>
+      </c>
+      <c r="Q109" s="56">
+        <f t="shared" si="35"/>
+        <v>3.4983230673732831E-2</v>
+      </c>
+      <c r="R109" s="56">
+        <f t="shared" si="35"/>
+        <v>3.4983230673732831E-2</v>
+      </c>
+      <c r="S109" s="56">
+        <f t="shared" si="35"/>
+        <v>3.4983230673732831E-2</v>
+      </c>
+      <c r="T109" s="56">
+        <f t="shared" si="35"/>
+        <v>6.1588267244131557E-2</v>
+      </c>
+      <c r="U109" s="56">
+        <f t="shared" si="35"/>
+        <v>6.1588267244131557E-2</v>
+      </c>
+      <c r="V109" s="56">
+        <f t="shared" si="35"/>
+        <v>6.1588267244131557E-2</v>
+      </c>
+      <c r="W109" s="56">
+        <f t="shared" si="35"/>
+        <v>6.1588267244131557E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="2:38">
+      <c r="B110" s="59" t="str">
+        <f t="shared" si="32"/>
+        <v>Peternakan</v>
+      </c>
+    </row>
+    <row r="111" spans="2:38">
+      <c r="B111" s="59" t="str">
+        <f t="shared" si="32"/>
+        <v>Jasa Pertanian dan Perburuan</v>
+      </c>
+    </row>
+    <row r="112" spans="2:38">
+      <c r="B112" s="59" t="str">
+        <f t="shared" si="32"/>
+        <v>Kehutanan dan Penebangan Kayu</v>
+      </c>
+    </row>
+    <row r="113" spans="2:23">
+      <c r="B113" s="52" t="str">
+        <f t="shared" si="32"/>
+        <v>Perikanan</v>
+      </c>
+      <c r="H113" s="56">
         <f>H101</f>
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <f t="shared" ref="J101:K101" si="29">I101</f>
-        <v>0</v>
-      </c>
-      <c r="K101">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="L101">
-        <f>L99*L100</f>
-        <v>0</v>
-      </c>
-      <c r="M101">
-        <f>L101</f>
-        <v>0</v>
-      </c>
-      <c r="N101">
-        <f t="shared" ref="N101:O101" si="30">M101</f>
-        <v>0</v>
-      </c>
-      <c r="O101">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="P101">
-        <f>P99*P100</f>
-        <v>0</v>
-      </c>
-      <c r="Q101">
-        <f>P101</f>
-        <v>0</v>
-      </c>
-      <c r="R101">
-        <f t="shared" ref="R101:S101" si="31">Q101</f>
-        <v>0</v>
-      </c>
-      <c r="S101">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="T101">
-        <f>T99*T100</f>
-        <v>0</v>
-      </c>
-      <c r="U101">
-        <f>T101</f>
-        <v>0</v>
-      </c>
-      <c r="V101">
-        <f t="shared" ref="V101:W101" si="32">U101</f>
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
+        <v>3.2000000000000015E-3</v>
+      </c>
+      <c r="I113" s="56">
+        <f t="shared" ref="I113:W113" si="36">I101</f>
+        <v>4.100266666666668E-3</v>
+      </c>
+      <c r="J113" s="56">
+        <f t="shared" si="36"/>
+        <v>5.0005333333333355E-3</v>
+      </c>
+      <c r="K113" s="56">
+        <f t="shared" si="36"/>
+        <v>5.9008000000000021E-3</v>
+      </c>
+      <c r="L113" s="56">
+        <f t="shared" si="36"/>
+        <v>6.8010666666666686E-3</v>
+      </c>
+      <c r="M113" s="56">
+        <f t="shared" si="36"/>
+        <v>7.7013333333333361E-3</v>
+      </c>
+      <c r="N113" s="56">
+        <f t="shared" si="36"/>
+        <v>8.6016000000000026E-3</v>
+      </c>
+      <c r="O113" s="56">
+        <f t="shared" si="36"/>
+        <v>9.5018666666666692E-3</v>
+      </c>
+      <c r="P113" s="56">
+        <f t="shared" si="36"/>
+        <v>1.0402133333333336E-2</v>
+      </c>
+      <c r="Q113" s="56">
+        <f t="shared" si="36"/>
+        <v>1.1302400000000002E-2</v>
+      </c>
+      <c r="R113" s="56">
+        <f t="shared" si="36"/>
+        <v>1.2202666666666669E-2</v>
+      </c>
+      <c r="S113" s="56">
+        <f t="shared" si="36"/>
+        <v>1.3102933333333337E-2</v>
+      </c>
+      <c r="T113" s="56">
+        <f t="shared" si="36"/>
+        <v>1.4003200000000004E-2</v>
+      </c>
+      <c r="U113" s="56">
+        <f t="shared" si="36"/>
+        <v>1.490346666666667E-2</v>
+      </c>
+      <c r="V113" s="56">
+        <f t="shared" si="36"/>
+        <v>1.5803733333333337E-2</v>
+      </c>
+      <c r="W113" s="56">
+        <f t="shared" si="36"/>
+        <v>1.6704000000000004E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="2:23">
+      <c r="B114" s="52"/>
+    </row>
+    <row r="115" spans="2:23">
+      <c r="B115" s="52"/>
+    </row>
+    <row r="116" spans="2:23">
+      <c r="B116" s="52"/>
+    </row>
+    <row r="117" spans="2:23">
+      <c r="B117" s="52"/>
+    </row>
+    <row r="118" spans="2:23">
+      <c r="B118" s="52"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25154,7 +26283,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88870A17-6870-4B82-9195-5F86BAC001F4}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="str">
@@ -25384,7 +26513,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F124A65C-8B06-43F1-B0C3-15F34DAFEF8C}">
   <dimension ref="A1:X61"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" t="s">
@@ -25757,152 +26886,46 @@
       </c>
     </row>
     <row r="6" spans="1:24">
-      <c r="A6">
-        <v>302</v>
-      </c>
-      <c r="B6">
-        <v>51</v>
-      </c>
-      <c r="C6">
-        <v>33</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="37">
-        <v>1.0000000000000023E-2</v>
-      </c>
-      <c r="G6" s="37">
-        <v>1.500000000000002E-2</v>
-      </c>
-      <c r="H6" s="37">
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="I6" s="37">
-        <v>2.5000000000000015E-2</v>
-      </c>
-      <c r="J6" s="37">
-        <v>3.0000000000000013E-2</v>
-      </c>
-      <c r="K6" s="37">
-        <v>3.500000000000001E-2</v>
-      </c>
-      <c r="L6" s="37">
-        <v>4.0000000000000008E-2</v>
-      </c>
-      <c r="M6" s="37">
-        <v>4.5000000000000005E-2</v>
-      </c>
-      <c r="N6" s="37">
-        <v>0.05</v>
-      </c>
-      <c r="O6" s="37">
-        <v>5.5E-2</v>
-      </c>
-      <c r="P6" s="37">
-        <v>0.06</v>
-      </c>
-      <c r="Q6" s="37">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="R6" s="37">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="S6" s="37">
-        <v>7.4999999999999983E-2</v>
-      </c>
-      <c r="T6" s="37">
-        <v>7.9999999999999988E-2</v>
-      </c>
-      <c r="U6" s="37">
-        <v>8.4999999999999992E-2</v>
-      </c>
-      <c r="V6" s="37">
-        <v>0.09</v>
-      </c>
-      <c r="W6" s="37">
-        <v>9.4999999999999973E-2</v>
-      </c>
-      <c r="X6" s="37">
-        <v>9.9999999999999978E-2</v>
-      </c>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="37"/>
+      <c r="O6" s="37"/>
+      <c r="P6" s="37"/>
+      <c r="Q6" s="37"/>
+      <c r="R6" s="37"/>
+      <c r="S6" s="37"/>
+      <c r="T6" s="37"/>
+      <c r="U6" s="37"/>
+      <c r="V6" s="37"/>
+      <c r="W6" s="37"/>
+      <c r="X6" s="37"/>
     </row>
     <row r="7" spans="1:24">
-      <c r="A7">
-        <v>302</v>
-      </c>
-      <c r="B7">
-        <v>51</v>
-      </c>
-      <c r="C7">
-        <v>37</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="37">
-        <v>1.0000000000000023E-2</v>
-      </c>
-      <c r="G7" s="37">
-        <v>1.500000000000002E-2</v>
-      </c>
-      <c r="H7" s="37">
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="I7" s="37">
-        <v>2.5000000000000015E-2</v>
-      </c>
-      <c r="J7" s="37">
-        <v>3.0000000000000013E-2</v>
-      </c>
-      <c r="K7" s="37">
-        <v>3.500000000000001E-2</v>
-      </c>
-      <c r="L7" s="37">
-        <v>4.0000000000000008E-2</v>
-      </c>
-      <c r="M7" s="37">
-        <v>4.5000000000000005E-2</v>
-      </c>
-      <c r="N7" s="37">
-        <v>0.05</v>
-      </c>
-      <c r="O7" s="37">
-        <v>5.5E-2</v>
-      </c>
-      <c r="P7" s="37">
-        <v>0.06</v>
-      </c>
-      <c r="Q7" s="37">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="R7" s="37">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="S7" s="37">
-        <v>7.4999999999999983E-2</v>
-      </c>
-      <c r="T7" s="37">
-        <v>7.9999999999999988E-2</v>
-      </c>
-      <c r="U7" s="37">
-        <v>8.4999999999999992E-2</v>
-      </c>
-      <c r="V7" s="37">
-        <v>0.09</v>
-      </c>
-      <c r="W7" s="37">
-        <v>9.4999999999999973E-2</v>
-      </c>
-      <c r="X7" s="37">
-        <v>9.9999999999999978E-2</v>
-      </c>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37"/>
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="37"/>
+      <c r="S7" s="37"/>
+      <c r="T7" s="37"/>
+      <c r="U7" s="37"/>
+      <c r="V7" s="37"/>
+      <c r="W7" s="37"/>
+      <c r="X7" s="37"/>
     </row>
     <row r="14" spans="1:24">
       <c r="B14" t="s">
@@ -26002,7 +27025,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BC55"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:55" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -35197,7 +36220,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BC55"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:55" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -44392,7 +45415,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:BC55"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:55" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -53587,17 +54610,17 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M55"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="41.1796875" customWidth="1"/>
+    <col min="1" max="1" width="41.21875" customWidth="1"/>
     <col min="2" max="2" width="82" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1">
@@ -55863,10 +56886,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E56"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1">
@@ -56826,12 +57849,12 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="87.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="87.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="91.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="91.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1">
@@ -57629,33 +58652,33 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:CQ64"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="82" bestFit="1" customWidth="1"/>
-    <col min="46" max="47" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="53" max="54" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="55" max="56" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="58" max="59" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="64" max="65" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="68" max="69" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="71" max="75" width="13.08984375" customWidth="1"/>
-    <col min="76" max="79" width="11.81640625" customWidth="1"/>
-    <col min="80" max="80" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="81" max="87" width="9.36328125" customWidth="1"/>
+    <col min="46" max="47" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="53" max="54" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="55" max="56" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="58" max="59" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="64" max="65" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="68" max="69" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="71" max="75" width="13.109375" customWidth="1"/>
+    <col min="76" max="79" width="11.77734375" customWidth="1"/>
+    <col min="80" max="80" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="81" max="87" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:95" s="38" customFormat="1" ht="87">
+    <row r="1" spans="1:95" s="38" customFormat="1" ht="86.4">
       <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
@@ -57899,33 +58922,33 @@
       <c r="CD1" s="39" t="s">
         <v>449</v>
       </c>
-      <c r="CE1" s="52" t="s">
+      <c r="CE1" s="57" t="s">
         <v>450</v>
       </c>
-      <c r="CF1" s="52"/>
-      <c r="CG1" s="52"/>
+      <c r="CF1" s="57"/>
+      <c r="CG1" s="57"/>
       <c r="CH1" s="39" t="s">
         <v>502</v>
       </c>
       <c r="CI1" s="39" t="s">
         <v>449</v>
       </c>
-      <c r="CJ1" s="52" t="s">
+      <c r="CJ1" s="57" t="s">
         <v>450</v>
       </c>
-      <c r="CK1" s="52"/>
-      <c r="CL1" s="52"/>
+      <c r="CK1" s="57"/>
+      <c r="CL1" s="57"/>
       <c r="CM1" s="39" t="s">
         <v>502</v>
       </c>
       <c r="CN1" s="39" t="s">
         <v>449</v>
       </c>
-      <c r="CO1" s="52" t="s">
+      <c r="CO1" s="57" t="s">
         <v>450</v>
       </c>
-      <c r="CP1" s="52"/>
-      <c r="CQ1" s="52"/>
+      <c r="CP1" s="57"/>
+      <c r="CQ1" s="57"/>
     </row>
     <row r="2" spans="1:95">
       <c r="A2" t="s">
@@ -73282,13 +74305,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26A35B88-9AE2-4105-B20E-CD1011224290}">
   <dimension ref="A1:N62"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="91.36328125" customWidth="1"/>
-    <col min="2" max="7" width="13.453125" customWidth="1"/>
-    <col min="8" max="12" width="11.6328125" customWidth="1"/>
-    <col min="13" max="13" width="16.08984375" customWidth="1"/>
-    <col min="14" max="14" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="91.33203125" customWidth="1"/>
+    <col min="2" max="7" width="13.44140625" customWidth="1"/>
+    <col min="8" max="12" width="11.6640625" customWidth="1"/>
+    <col min="13" max="13" width="16.109375" customWidth="1"/>
+    <col min="14" max="14" width="19.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -76457,17 +77480,17 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:I56"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="87.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="87.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
-    <col min="5" max="5" width="58.90625" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.88671875" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1">
@@ -78105,14 +79128,14 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.08984375" customWidth="1"/>
-    <col min="3" max="11" width="16.08984375" customWidth="1"/>
-    <col min="12" max="12" width="4.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" customWidth="1"/>
+    <col min="3" max="11" width="16.109375" customWidth="1"/>
+    <col min="12" max="12" width="4.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="22" customFormat="1" ht="43.5">
+    <row r="1" spans="1:12" s="22" customFormat="1" ht="43.2">
       <c r="A1" s="26" t="s">
         <v>362</v>
       </c>
@@ -78671,13 +79694,13 @@
       <c r="E30" s="23"/>
     </row>
     <row r="31" spans="1:12" ht="286.5" customHeight="1">
-      <c r="A31" s="53" t="s">
+      <c r="A31" s="58" t="s">
         <v>446</v>
       </c>
-      <c r="B31" s="53"/>
-      <c r="C31" s="53"/>
-      <c r="D31" s="53"/>
-      <c r="E31" s="53"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -78693,10 +79716,10 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:AF60"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.81640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="32" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="32" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32">
@@ -84784,11 +85807,11 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:AF60"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="23" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="24" max="27" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="23" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="24" max="27" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="28" max="32" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -90874,14 +91897,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01798009-0DF6-4BB3-B890-CF30441E949E}">
   <dimension ref="A1:AF31"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="16" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.81640625" customWidth="1"/>
-    <col min="18" max="21" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="22" max="32" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="16" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.77734375" customWidth="1"/>
+    <col min="18" max="21" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="22" max="32" width="11.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32">
@@ -91080,7 +92103,7 @@
         <v>10495720</v>
       </c>
     </row>
-    <row r="3" spans="1:32" ht="15.5">
+    <row r="3" spans="1:32" ht="15.6">
       <c r="A3" s="42"/>
     </row>
     <row r="4" spans="1:32">
@@ -91091,7 +92114,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="5" spans="1:32" ht="15.5">
+    <row r="5" spans="1:32" ht="15.6">
       <c r="A5" s="42"/>
       <c r="D5" s="44"/>
       <c r="E5" s="44"/>
@@ -91118,10 +92141,10 @@
       <c r="Z5" s="44"/>
       <c r="AA5" s="44"/>
     </row>
-    <row r="6" spans="1:32" ht="15.5">
+    <row r="6" spans="1:32" ht="15.6">
       <c r="A6" s="42"/>
     </row>
-    <row r="7" spans="1:32" ht="15.5">
+    <row r="7" spans="1:32" ht="15.6">
       <c r="A7" s="42"/>
       <c r="Q7" s="43"/>
     </row>
@@ -91317,7 +92340,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E13E0A2-E10C-4D48-A433-9FA5EF0BD6D5}">
   <dimension ref="A1:L56"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
@@ -93455,14 +94478,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6324EDC2-2880-4DCF-ACF6-5EBE3C11CE1C}">
   <dimension ref="A1:AE61"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="35.1796875" customWidth="1"/>
-    <col min="3" max="3" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.21875" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
